--- a/data/seat/03-marzo 2026.xlsx
+++ b/data/seat/03-marzo 2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Filezilla/2021/Energia/2026/marzo/31-03-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoefe-my.sharepoint.com/personal/mvara_efevalparaiso_cl/Documents/Datos/Energía/SEAT/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{ECD9FC00-F36C-4054-8AB9-7B3D04D309C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8637FD2-5069-434C-9C1B-C486F1C75A28}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{ECD9FC00-F36C-4054-8AB9-7B3D04D309C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9220140E-3076-419B-A281-3CCB4F243450}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SEAT-SERs" sheetId="1" r:id="rId1"/>
@@ -2053,6 +2053,60 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="58" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2083,39 +2137,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2128,31 +2149,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3438,40 +3438,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>21804.16</c:v>
+                  <c:v>21677.16</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47750</c:v>
+                  <c:v>47623</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>44617</c:v>
+                  <c:v>44490</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>51884</c:v>
+                  <c:v>51757</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>52083</c:v>
+                  <c:v>51956</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52091</c:v>
+                  <c:v>51964</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>27775.760000000002</c:v>
+                  <c:v>27648.760000000002</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25714</c:v>
+                  <c:v>25587</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>46909</c:v>
+                  <c:v>46782</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>47509</c:v>
+                  <c:v>47382</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>50143</c:v>
+                  <c:v>50016</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>50662</c:v>
+                  <c:v>50535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3728,40 +3728,40 @@
                 <c:formatCode>#,##0\ "Kwh"</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>7263.84</c:v>
+                  <c:v>7390.84</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7740</c:v>
+                  <c:v>7867</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>7832</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>7705</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>7578</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>7459</c:v>
+                  <c:v>7586</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7339</c:v>
+                  <c:v>7466</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7248.24</c:v>
+                  <c:v>7375.24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7228</c:v>
+                  <c:v>7355</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7591</c:v>
+                  <c:v>7718</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7691</c:v>
+                  <c:v>7818</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7735</c:v>
+                  <c:v>7862</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7744</c:v>
+                  <c:v>7871</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6959,7 +6959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BW41"/>
+  <dimension ref="A1:BV41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.28515625" style="134" customWidth="1"/>
@@ -7017,297 +7017,297 @@
     <col min="74" max="16384" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75" s="133" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:74" s="133" customFormat="1" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="127">
         <v>1.1111111E+55</v>
       </c>
-      <c r="B1" s="183" t="s">
+      <c r="B1" s="201" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="128"/>
-      <c r="D1" s="185" t="s">
+      <c r="D1" s="203" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
-      <c r="H1" s="186"/>
-      <c r="I1" s="186"/>
-      <c r="J1" s="186"/>
-      <c r="K1" s="186"/>
-      <c r="L1" s="186"/>
-      <c r="M1" s="186"/>
-      <c r="N1" s="186"/>
-      <c r="O1" s="187"/>
-      <c r="P1" s="188"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
+      <c r="I1" s="204"/>
+      <c r="J1" s="204"/>
+      <c r="K1" s="204"/>
+      <c r="L1" s="204"/>
+      <c r="M1" s="204"/>
+      <c r="N1" s="204"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="206"/>
       <c r="Q1" s="129"/>
-      <c r="R1" s="193" t="s">
+      <c r="R1" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="194"/>
-      <c r="AA1" s="195"/>
+      <c r="S1" s="184"/>
+      <c r="T1" s="184"/>
+      <c r="U1" s="184"/>
+      <c r="V1" s="184"/>
+      <c r="W1" s="184"/>
+      <c r="X1" s="184"/>
+      <c r="Y1" s="184"/>
+      <c r="Z1" s="184"/>
+      <c r="AA1" s="185"/>
       <c r="AB1" s="130"/>
-      <c r="AC1" s="193" t="s">
+      <c r="AC1" s="183" t="s">
         <v>3</v>
       </c>
-      <c r="AD1" s="194"/>
-      <c r="AE1" s="194"/>
-      <c r="AF1" s="194"/>
-      <c r="AG1" s="194"/>
-      <c r="AH1" s="194"/>
-      <c r="AI1" s="194"/>
-      <c r="AJ1" s="194"/>
-      <c r="AK1" s="195"/>
+      <c r="AD1" s="184"/>
+      <c r="AE1" s="184"/>
+      <c r="AF1" s="184"/>
+      <c r="AG1" s="184"/>
+      <c r="AH1" s="184"/>
+      <c r="AI1" s="184"/>
+      <c r="AJ1" s="184"/>
+      <c r="AK1" s="185"/>
       <c r="AL1" s="131"/>
-      <c r="AM1" s="193" t="s">
+      <c r="AM1" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="194"/>
-      <c r="AO1" s="194"/>
-      <c r="AP1" s="194"/>
-      <c r="AQ1" s="194"/>
-      <c r="AR1" s="194"/>
-      <c r="AS1" s="194"/>
-      <c r="AT1" s="194"/>
-      <c r="AU1" s="195"/>
+      <c r="AN1" s="184"/>
+      <c r="AO1" s="184"/>
+      <c r="AP1" s="184"/>
+      <c r="AQ1" s="184"/>
+      <c r="AR1" s="184"/>
+      <c r="AS1" s="184"/>
+      <c r="AT1" s="184"/>
+      <c r="AU1" s="185"/>
       <c r="AV1" s="131"/>
-      <c r="AW1" s="193" t="s">
+      <c r="AW1" s="183" t="s">
         <v>57</v>
       </c>
-      <c r="AX1" s="194"/>
-      <c r="AY1" s="194"/>
-      <c r="AZ1" s="194"/>
-      <c r="BA1" s="194"/>
-      <c r="BB1" s="194"/>
-      <c r="BC1" s="194"/>
-      <c r="BD1" s="194"/>
-      <c r="BE1" s="194"/>
-      <c r="BF1" s="194"/>
-      <c r="BG1" s="194"/>
-      <c r="BH1" s="195"/>
+      <c r="AX1" s="184"/>
+      <c r="AY1" s="184"/>
+      <c r="AZ1" s="184"/>
+      <c r="BA1" s="184"/>
+      <c r="BB1" s="184"/>
+      <c r="BC1" s="184"/>
+      <c r="BD1" s="184"/>
+      <c r="BE1" s="184"/>
+      <c r="BF1" s="184"/>
+      <c r="BG1" s="184"/>
+      <c r="BH1" s="185"/>
       <c r="BI1" s="131"/>
-      <c r="BJ1" s="193" t="s">
+      <c r="BJ1" s="183" t="s">
         <v>5</v>
       </c>
-      <c r="BK1" s="194"/>
-      <c r="BL1" s="194"/>
-      <c r="BM1" s="194"/>
-      <c r="BN1" s="194"/>
-      <c r="BO1" s="194"/>
-      <c r="BP1" s="194"/>
-      <c r="BQ1" s="194"/>
-      <c r="BR1" s="195"/>
+      <c r="BK1" s="184"/>
+      <c r="BL1" s="184"/>
+      <c r="BM1" s="184"/>
+      <c r="BN1" s="184"/>
+      <c r="BO1" s="184"/>
+      <c r="BP1" s="184"/>
+      <c r="BQ1" s="184"/>
+      <c r="BR1" s="185"/>
       <c r="BS1" s="132"/>
     </row>
-    <row r="2" spans="1:75" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="183"/>
+    <row r="2" spans="1:74" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="201"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="190"/>
-      <c r="F2" s="190"/>
-      <c r="G2" s="190"/>
-      <c r="H2" s="190"/>
-      <c r="I2" s="190"/>
-      <c r="J2" s="190"/>
-      <c r="K2" s="190"/>
-      <c r="L2" s="190"/>
-      <c r="M2" s="190"/>
-      <c r="N2" s="190"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="192"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="208"/>
+      <c r="I2" s="208"/>
+      <c r="J2" s="208"/>
+      <c r="K2" s="208"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="209"/>
+      <c r="P2" s="210"/>
       <c r="Q2" s="58"/>
-      <c r="R2" s="196"/>
-      <c r="S2" s="197"/>
-      <c r="T2" s="197"/>
-      <c r="U2" s="197"/>
-      <c r="V2" s="197"/>
-      <c r="W2" s="197"/>
-      <c r="X2" s="197"/>
-      <c r="Y2" s="197"/>
-      <c r="Z2" s="197"/>
-      <c r="AA2" s="198"/>
+      <c r="R2" s="186"/>
+      <c r="S2" s="187"/>
+      <c r="T2" s="187"/>
+      <c r="U2" s="187"/>
+      <c r="V2" s="187"/>
+      <c r="W2" s="187"/>
+      <c r="X2" s="187"/>
+      <c r="Y2" s="187"/>
+      <c r="Z2" s="187"/>
+      <c r="AA2" s="188"/>
       <c r="AB2" s="60"/>
-      <c r="AC2" s="196"/>
-      <c r="AD2" s="197"/>
-      <c r="AE2" s="197"/>
-      <c r="AF2" s="197"/>
-      <c r="AG2" s="197"/>
-      <c r="AH2" s="197"/>
-      <c r="AI2" s="197"/>
-      <c r="AJ2" s="197"/>
-      <c r="AK2" s="198"/>
+      <c r="AC2" s="186"/>
+      <c r="AD2" s="187"/>
+      <c r="AE2" s="187"/>
+      <c r="AF2" s="187"/>
+      <c r="AG2" s="187"/>
+      <c r="AH2" s="187"/>
+      <c r="AI2" s="187"/>
+      <c r="AJ2" s="187"/>
+      <c r="AK2" s="188"/>
       <c r="AL2" s="59"/>
-      <c r="AM2" s="196"/>
-      <c r="AN2" s="197"/>
-      <c r="AO2" s="197"/>
-      <c r="AP2" s="197"/>
-      <c r="AQ2" s="197"/>
-      <c r="AR2" s="197"/>
-      <c r="AS2" s="197"/>
-      <c r="AT2" s="197"/>
-      <c r="AU2" s="198"/>
+      <c r="AM2" s="186"/>
+      <c r="AN2" s="187"/>
+      <c r="AO2" s="187"/>
+      <c r="AP2" s="187"/>
+      <c r="AQ2" s="187"/>
+      <c r="AR2" s="187"/>
+      <c r="AS2" s="187"/>
+      <c r="AT2" s="187"/>
+      <c r="AU2" s="188"/>
       <c r="AV2" s="59"/>
-      <c r="AW2" s="196"/>
-      <c r="AX2" s="197"/>
-      <c r="AY2" s="197"/>
-      <c r="AZ2" s="197"/>
-      <c r="BA2" s="197"/>
-      <c r="BB2" s="197"/>
-      <c r="BC2" s="197"/>
-      <c r="BD2" s="197"/>
-      <c r="BE2" s="197"/>
-      <c r="BF2" s="197"/>
-      <c r="BG2" s="197"/>
-      <c r="BH2" s="198"/>
+      <c r="AW2" s="186"/>
+      <c r="AX2" s="187"/>
+      <c r="AY2" s="187"/>
+      <c r="AZ2" s="187"/>
+      <c r="BA2" s="187"/>
+      <c r="BB2" s="187"/>
+      <c r="BC2" s="187"/>
+      <c r="BD2" s="187"/>
+      <c r="BE2" s="187"/>
+      <c r="BF2" s="187"/>
+      <c r="BG2" s="187"/>
+      <c r="BH2" s="188"/>
       <c r="BI2" s="59"/>
-      <c r="BJ2" s="196"/>
-      <c r="BK2" s="197"/>
-      <c r="BL2" s="197"/>
-      <c r="BM2" s="197"/>
-      <c r="BN2" s="197"/>
-      <c r="BO2" s="197"/>
-      <c r="BP2" s="197"/>
-      <c r="BQ2" s="197"/>
-      <c r="BR2" s="198"/>
+      <c r="BJ2" s="186"/>
+      <c r="BK2" s="187"/>
+      <c r="BL2" s="187"/>
+      <c r="BM2" s="187"/>
+      <c r="BN2" s="187"/>
+      <c r="BO2" s="187"/>
+      <c r="BP2" s="187"/>
+      <c r="BQ2" s="187"/>
+      <c r="BR2" s="188"/>
       <c r="BS2" s="135"/>
     </row>
-    <row r="3" spans="1:75" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="183"/>
+    <row r="3" spans="1:74" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="201"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="202" t="s">
+      <c r="D3" s="189" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="202" t="s">
+      <c r="E3" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="202" t="s">
+      <c r="F3" s="189" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="202" t="s">
+      <c r="G3" s="189" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="202" t="s">
+      <c r="H3" s="189" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="204" t="s">
+      <c r="I3" s="211" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="205"/>
-      <c r="K3" s="206"/>
-      <c r="L3" s="207"/>
-      <c r="M3" s="204" t="s">
+      <c r="J3" s="212"/>
+      <c r="K3" s="213"/>
+      <c r="L3" s="214"/>
+      <c r="M3" s="211" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="205"/>
-      <c r="O3" s="206"/>
-      <c r="P3" s="207"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="213"/>
+      <c r="P3" s="214"/>
       <c r="Q3" s="58"/>
-      <c r="R3" s="208" t="s">
+      <c r="R3" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="S3" s="200"/>
-      <c r="T3" s="209"/>
-      <c r="U3" s="209"/>
-      <c r="V3" s="208" t="s">
+      <c r="S3" s="194"/>
+      <c r="T3" s="215"/>
+      <c r="U3" s="215"/>
+      <c r="V3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="W3" s="200"/>
-      <c r="X3" s="200"/>
-      <c r="Y3" s="200"/>
-      <c r="Z3" s="200"/>
-      <c r="AA3" s="201"/>
+      <c r="W3" s="194"/>
+      <c r="X3" s="194"/>
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="195"/>
       <c r="AB3" s="60"/>
-      <c r="AC3" s="210" t="s">
+      <c r="AC3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="AD3" s="212" t="s">
+      <c r="AD3" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="AE3" s="208" t="s">
+      <c r="AE3" s="193" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="200"/>
-      <c r="AG3" s="201"/>
-      <c r="AH3" s="208" t="s">
+      <c r="AF3" s="194"/>
+      <c r="AG3" s="195"/>
+      <c r="AH3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="AI3" s="200"/>
-      <c r="AJ3" s="200"/>
-      <c r="AK3" s="201"/>
+      <c r="AI3" s="194"/>
+      <c r="AJ3" s="194"/>
+      <c r="AK3" s="195"/>
       <c r="AL3" s="59"/>
-      <c r="AM3" s="213" t="s">
+      <c r="AM3" s="196" t="s">
         <v>15</v>
       </c>
-      <c r="AN3" s="210" t="s">
+      <c r="AN3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="AO3" s="199" t="s">
+      <c r="AO3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AP3" s="200"/>
-      <c r="AQ3" s="201"/>
-      <c r="AR3" s="208" t="s">
+      <c r="AP3" s="194"/>
+      <c r="AQ3" s="195"/>
+      <c r="AR3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="AS3" s="200"/>
-      <c r="AT3" s="200"/>
-      <c r="AU3" s="201"/>
+      <c r="AS3" s="194"/>
+      <c r="AT3" s="194"/>
+      <c r="AU3" s="195"/>
       <c r="AV3" s="59"/>
-      <c r="AW3" s="210" t="s">
+      <c r="AW3" s="191" t="s">
         <v>15</v>
       </c>
-      <c r="AX3" s="210" t="s">
+      <c r="AX3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="199" t="s">
+      <c r="AY3" s="200" t="s">
         <v>13</v>
       </c>
-      <c r="AZ3" s="199"/>
-      <c r="BA3" s="200"/>
-      <c r="BB3" s="201"/>
-      <c r="BC3" s="208" t="s">
+      <c r="AZ3" s="200"/>
+      <c r="BA3" s="194"/>
+      <c r="BB3" s="195"/>
+      <c r="BC3" s="193" t="s">
         <v>14</v>
       </c>
-      <c r="BD3" s="199"/>
-      <c r="BE3" s="199"/>
-      <c r="BF3" s="200"/>
-      <c r="BG3" s="200"/>
-      <c r="BH3" s="201"/>
+      <c r="BD3" s="200"/>
+      <c r="BE3" s="200"/>
+      <c r="BF3" s="194"/>
+      <c r="BG3" s="194"/>
+      <c r="BH3" s="195"/>
       <c r="BI3" s="59"/>
-      <c r="BJ3" s="213" t="s">
+      <c r="BJ3" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="BK3" s="210" t="s">
+      <c r="BK3" s="191" t="s">
         <v>17</v>
       </c>
-      <c r="BL3" s="214" t="s">
+      <c r="BL3" s="197" t="s">
         <v>18</v>
       </c>
-      <c r="BM3" s="215"/>
-      <c r="BN3" s="216"/>
-      <c r="BO3" s="199" t="s">
+      <c r="BM3" s="198"/>
+      <c r="BN3" s="199"/>
+      <c r="BO3" s="200" t="s">
         <v>14</v>
       </c>
-      <c r="BP3" s="200"/>
-      <c r="BQ3" s="200"/>
-      <c r="BR3" s="201"/>
+      <c r="BP3" s="194"/>
+      <c r="BQ3" s="194"/>
+      <c r="BR3" s="195"/>
       <c r="BS3" s="135"/>
     </row>
-    <row r="4" spans="1:75" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="184"/>
+    <row r="4" spans="1:74" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="202"/>
       <c r="C4" s="2"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="203"/>
+      <c r="D4" s="190"/>
+      <c r="E4" s="190"/>
+      <c r="F4" s="190"/>
+      <c r="G4" s="190"/>
+      <c r="H4" s="190"/>
       <c r="I4" s="80" t="s">
         <v>3</v>
       </c>
@@ -7364,8 +7364,8 @@
         <v>24</v>
       </c>
       <c r="AB4" s="60"/>
-      <c r="AC4" s="211"/>
-      <c r="AD4" s="194"/>
+      <c r="AC4" s="192"/>
+      <c r="AD4" s="184"/>
       <c r="AE4" s="62" t="s">
         <v>27</v>
       </c>
@@ -7388,8 +7388,8 @@
         <v>24</v>
       </c>
       <c r="AL4" s="61"/>
-      <c r="AM4" s="193"/>
-      <c r="AN4" s="211"/>
+      <c r="AM4" s="183"/>
+      <c r="AN4" s="192"/>
       <c r="AO4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7412,8 +7412,8 @@
         <v>24</v>
       </c>
       <c r="AV4" s="61"/>
-      <c r="AW4" s="211"/>
-      <c r="AX4" s="211"/>
+      <c r="AW4" s="192"/>
+      <c r="AX4" s="192"/>
       <c r="AY4" s="123" t="s">
         <v>27</v>
       </c>
@@ -7445,8 +7445,8 @@
         <v>24</v>
       </c>
       <c r="BI4" s="61"/>
-      <c r="BJ4" s="193"/>
-      <c r="BK4" s="211"/>
+      <c r="BJ4" s="183"/>
+      <c r="BK4" s="192"/>
       <c r="BL4" s="123" t="s">
         <v>32</v>
       </c>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="BS4" s="136"/>
     </row>
-    <row r="5" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="137"/>
       <c r="C5" s="138"/>
       <c r="D5" s="83"/>
@@ -7542,7 +7542,7 @@
       <c r="BR5" s="66"/>
       <c r="BS5" s="145"/>
     </row>
-    <row r="6" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="56">
         <v>46081</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>0.65416666666666667</v>
       </c>
     </row>
-    <row r="7" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="166"/>
       <c r="B7" s="56">
         <f>B6+1</f>
@@ -7792,19 +7792,19 @@
       </c>
       <c r="E7" s="159">
         <f t="shared" ref="E7:E10" si="23">F7/D7</f>
-        <v>0.75010871060960504</v>
+        <v>0.74573964497041423</v>
       </c>
       <c r="F7" s="87">
         <f t="shared" ref="F7:F37" si="24">D7-H7</f>
-        <v>21804.16</v>
+        <v>21677.16</v>
       </c>
       <c r="G7" s="159">
         <f t="shared" ref="G7:G10" si="25">H7/D7</f>
-        <v>0.24989128939039493</v>
+        <v>0.25426035502958583</v>
       </c>
       <c r="H7" s="146">
         <f t="shared" ref="H7:H37" si="26">U7+AG7+AQ7+BB7</f>
-        <v>7263.84</v>
+        <v>7390.84</v>
       </c>
       <c r="I7" s="160">
         <f t="shared" ref="I7:I10" si="27">AE7/(AE7+AO7+BL7+AY7)</f>
@@ -7946,11 +7946,11 @@
       </c>
       <c r="AW7" s="110">
         <f t="shared" ref="AW7:AW10" si="42">BA7/AZ7</f>
-        <v>0.24099891891891889</v>
+        <v>0.21353945945945943</v>
       </c>
       <c r="AX7" s="110">
         <f t="shared" ref="AX7:AX10" si="43">BB7/AZ7</f>
-        <v>0.75900108108108111</v>
+        <v>0.7864605405405406</v>
       </c>
       <c r="AY7" s="111">
         <f t="shared" si="17"/>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="BA7" s="120">
         <f t="shared" si="18"/>
-        <v>1114.6199999999999</v>
+        <v>987.61999999999989</v>
       </c>
       <c r="BB7" s="113">
-        <f>2939.38+571</f>
-        <v>3510.38</v>
+        <f>2939.38+698</f>
+        <v>3637.38</v>
       </c>
       <c r="BC7" s="112">
         <v>1846.59</v>
@@ -8019,18 +8019,9 @@
       <c r="BR7" s="157">
         <v>0.87152777777777779</v>
       </c>
-      <c r="BT7" s="14">
-        <v>7263.84</v>
-      </c>
-      <c r="BV7" s="175">
-        <f>BT7-H7</f>
-        <v>0</v>
-      </c>
-      <c r="BW7" s="14">
-        <v>571</v>
-      </c>
+      <c r="BV7" s="175"/>
     </row>
-    <row r="8" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="166"/>
       <c r="B8" s="56">
         <f t="shared" ref="B8:B37" si="47">B7+1</f>
@@ -8043,19 +8034,19 @@
       </c>
       <c r="E8" s="159">
         <f t="shared" si="23"/>
-        <v>0.8605154081816544</v>
+        <v>0.85822670751486752</v>
       </c>
       <c r="F8" s="87">
         <f t="shared" si="24"/>
-        <v>47750</v>
+        <v>47623</v>
       </c>
       <c r="G8" s="159">
         <f t="shared" si="25"/>
-        <v>0.13948459181834566</v>
+        <v>0.14177329248513246</v>
       </c>
       <c r="H8" s="146">
         <f t="shared" si="26"/>
-        <v>7740</v>
+        <v>7867</v>
       </c>
       <c r="I8" s="160">
         <f t="shared" si="27"/>
@@ -8197,11 +8188,11 @@
       </c>
       <c r="AW8" s="110">
         <f t="shared" si="42"/>
-        <v>0.60544738569240864</v>
+        <v>0.59155545832421785</v>
       </c>
       <c r="AX8" s="110">
         <f t="shared" si="43"/>
-        <v>0.39455261430759131</v>
+        <v>0.40844454167578209</v>
       </c>
       <c r="AY8" s="111">
         <f t="shared" si="17"/>
@@ -8212,11 +8203,11 @@
       </c>
       <c r="BA8" s="120">
         <f t="shared" si="18"/>
-        <v>5535</v>
+        <v>5408</v>
       </c>
       <c r="BB8" s="113">
-        <f>3036+571</f>
-        <v>3607</v>
+        <f>3036+698</f>
+        <v>3734</v>
       </c>
       <c r="BC8" s="112">
         <v>4368</v>
@@ -8270,15 +8261,9 @@
       <c r="BR8" s="157">
         <v>0.73958333333333337</v>
       </c>
-      <c r="BT8" s="14">
-        <v>7740</v>
-      </c>
-      <c r="BV8" s="175">
-        <f t="shared" ref="BV8:BV21" si="52">BT8-H8</f>
-        <v>0</v>
-      </c>
+      <c r="BV8" s="175"/>
     </row>
-    <row r="9" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="166" t="s">
         <v>67</v>
       </c>
@@ -8293,19 +8278,19 @@
       </c>
       <c r="E9" s="159">
         <f t="shared" si="23"/>
-        <v>0.85273880967852911</v>
+        <v>0.85031153243377544</v>
       </c>
       <c r="F9" s="87">
         <f t="shared" si="24"/>
-        <v>44617</v>
+        <v>44490</v>
       </c>
       <c r="G9" s="159">
         <f t="shared" si="25"/>
-        <v>0.14726119032147089</v>
+        <v>0.14968846756622453</v>
       </c>
       <c r="H9" s="146">
         <f t="shared" si="26"/>
-        <v>7705</v>
+        <v>7832</v>
       </c>
       <c r="I9" s="160">
         <f t="shared" si="27"/>
@@ -8447,11 +8432,11 @@
       </c>
       <c r="AW9" s="110">
         <f t="shared" si="42"/>
-        <v>0.60481555113761876</v>
+        <v>0.59078860172299541</v>
       </c>
       <c r="AX9" s="110">
         <f t="shared" si="43"/>
-        <v>0.39518444886238124</v>
+        <v>0.40921139827700465</v>
       </c>
       <c r="AY9" s="111">
         <f t="shared" si="17"/>
@@ -8462,11 +8447,11 @@
       </c>
       <c r="BA9" s="120">
         <f t="shared" si="18"/>
-        <v>5476</v>
+        <v>5349</v>
       </c>
       <c r="BB9" s="113">
-        <f>3007+571</f>
-        <v>3578</v>
+        <f>3007+698</f>
+        <v>3705</v>
       </c>
       <c r="BC9" s="112">
         <v>4164</v>
@@ -8520,15 +8505,9 @@
       <c r="BR9" s="157">
         <v>0.76458333333333328</v>
       </c>
-      <c r="BT9" s="14">
-        <v>7705</v>
-      </c>
-      <c r="BV9" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV9" s="175"/>
     </row>
-    <row r="10" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="56">
         <f t="shared" si="47"/>
         <v>46085</v>
@@ -8540,19 +8519,19 @@
       </c>
       <c r="E10" s="159">
         <f t="shared" si="23"/>
-        <v>0.87255726346237938</v>
+        <v>0.87042144562914125</v>
       </c>
       <c r="F10" s="87">
         <f t="shared" si="24"/>
-        <v>51884</v>
+        <v>51757</v>
       </c>
       <c r="G10" s="159">
         <f t="shared" si="25"/>
-        <v>0.12744273653762067</v>
+        <v>0.12957855437085869</v>
       </c>
       <c r="H10" s="146">
         <f t="shared" si="26"/>
-        <v>7578</v>
+        <v>7705</v>
       </c>
       <c r="I10" s="160">
         <f t="shared" si="27"/>
@@ -8694,11 +8673,11 @@
       </c>
       <c r="AW10" s="110">
         <f t="shared" si="42"/>
-        <v>0.61187560949181929</v>
+        <v>0.59811463863907244</v>
       </c>
       <c r="AX10" s="110">
         <f t="shared" si="43"/>
-        <v>0.38812439050818076</v>
+        <v>0.40188536136092751</v>
       </c>
       <c r="AY10" s="111">
         <f t="shared" si="17"/>
@@ -8709,11 +8688,11 @@
       </c>
       <c r="BA10" s="120">
         <f t="shared" si="18"/>
-        <v>5647</v>
+        <v>5520</v>
       </c>
       <c r="BB10" s="113">
-        <f>3011+571</f>
-        <v>3582</v>
+        <f>3011+698</f>
+        <v>3709</v>
       </c>
       <c r="BC10" s="112">
         <v>3940</v>
@@ -8770,15 +8749,9 @@
       <c r="BS10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="BT10" s="14">
-        <v>7578</v>
-      </c>
-      <c r="BV10" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV10" s="175"/>
     </row>
-    <row r="11" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="56">
         <f t="shared" si="47"/>
         <v>46086</v>
@@ -8789,51 +8762,51 @@
         <v>59542</v>
       </c>
       <c r="E11" s="159">
-        <f t="shared" ref="E11:E24" si="53">F11/D11</f>
-        <v>0.87472708340331196</v>
+        <f t="shared" ref="E11:E24" si="52">F11/D11</f>
+        <v>0.87259413523227303</v>
       </c>
       <c r="F11" s="87">
         <f t="shared" si="24"/>
-        <v>52083</v>
+        <v>51956</v>
       </c>
       <c r="G11" s="159">
-        <f t="shared" ref="G11:G24" si="54">H11/D11</f>
-        <v>0.12527291659668804</v>
+        <f t="shared" ref="G11:G24" si="53">H11/D11</f>
+        <v>0.12740586476772697</v>
       </c>
       <c r="H11" s="146">
         <f t="shared" si="26"/>
-        <v>7459</v>
+        <v>7586</v>
       </c>
       <c r="I11" s="160">
-        <f t="shared" ref="I11:I24" si="55">AE11/(AE11+AO11+BL11+AY11)</f>
+        <f t="shared" ref="I11:I24" si="54">AE11/(AE11+AO11+BL11+AY11)</f>
         <v>0.10511600237953599</v>
       </c>
       <c r="J11" s="159">
-        <f t="shared" ref="J11:J24" si="56">AO11/(AE11+AO11+BL11+AY11)</f>
+        <f t="shared" ref="J11:J24" si="55">AO11/(AE11+AO11+BL11+AY11)</f>
         <v>0.14414039262343842</v>
       </c>
       <c r="K11" s="159">
-        <f t="shared" ref="K11:K24" si="57">AY11/(AF11+AP11+BM11+AZ11+AY11)</f>
+        <f t="shared" ref="K11:K24" si="56">AY11/(AF11+AP11+BM11+AZ11+AY11)</f>
         <v>0.15567461910330024</v>
       </c>
       <c r="L11" s="161">
-        <f t="shared" ref="L11:L24" si="58">BL11/(AE11+AO11+BL11+AY11)</f>
+        <f t="shared" ref="L11:L24" si="57">BL11/(AE11+AO11+BL11+AY11)</f>
         <v>0.61808447352766216</v>
       </c>
       <c r="M11" s="146">
-        <f t="shared" ref="M11:M24" si="59">(S11+T11)*I11</f>
+        <f t="shared" ref="M11:M24" si="58">(S11+T11)*I11</f>
         <v>6096.938370017846</v>
       </c>
       <c r="N11" s="146">
-        <f t="shared" ref="N11:N24" si="60">(S11+T11)*J11</f>
+        <f t="shared" ref="N11:N24" si="59">(S11+T11)*J11</f>
         <v>8360.4310529446757</v>
       </c>
       <c r="O11" s="146">
-        <f t="shared" ref="O11:O24" si="61">(S11+T11)*K11</f>
+        <f t="shared" ref="O11:O24" si="60">(S11+T11)*K11</f>
         <v>9029.4392572296201</v>
       </c>
       <c r="P11" s="146">
-        <f t="shared" ref="P11:P24" si="62">(S11+T11)*L11</f>
+        <f t="shared" ref="P11:P24" si="61">(S11+T11)*L11</f>
         <v>35850.135633551457</v>
       </c>
       <c r="Q11" s="56">
@@ -8875,11 +8848,11 @@
         <v>46086</v>
       </c>
       <c r="AC11" s="76">
-        <f t="shared" ref="AC11:AC25" si="63">+AF11/AE11</f>
+        <f t="shared" ref="AC11:AC25" si="62">+AF11/AE11</f>
         <v>1</v>
       </c>
       <c r="AD11" s="162">
-        <f t="shared" ref="AD11:AD25" si="64">+AG11/AE11</f>
+        <f t="shared" ref="AD11:AD25" si="63">+AG11/AE11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="163">
@@ -8909,11 +8882,11 @@
         <v>46086</v>
       </c>
       <c r="AM11" s="77">
-        <f t="shared" ref="AM11:AM25" si="65">+AP11/AO11</f>
+        <f t="shared" ref="AM11:AM25" si="64">+AP11/AO11</f>
         <v>0.59182831200990504</v>
       </c>
       <c r="AN11" s="76">
-        <f t="shared" ref="AN11:AN25" si="66">+AQ11/AO11</f>
+        <f t="shared" ref="AN11:AN25" si="65">+AQ11/AO11</f>
         <v>0.4081716879900949</v>
       </c>
       <c r="AO11" s="150">
@@ -8943,12 +8916,12 @@
         <v>46086</v>
       </c>
       <c r="AW11" s="110">
-        <f t="shared" ref="AW11:AW25" si="67">BA11/AZ11</f>
-        <v>0.60728699551569509</v>
+        <f t="shared" ref="AW11:AW25" si="66">BA11/AZ11</f>
+        <v>0.59304932735426008</v>
       </c>
       <c r="AX11" s="110">
-        <f t="shared" ref="AX11:AX25" si="68">BB11/AZ11</f>
-        <v>0.39271300448430491</v>
+        <f t="shared" ref="AX11:AX25" si="67">BB11/AZ11</f>
+        <v>0.40695067264573992</v>
       </c>
       <c r="AY11" s="111">
         <f t="shared" si="17"/>
@@ -8959,11 +8932,11 @@
       </c>
       <c r="BA11" s="120">
         <f t="shared" si="18"/>
-        <v>5417</v>
+        <v>5290</v>
       </c>
       <c r="BB11" s="113">
-        <f>2932+571</f>
-        <v>3503</v>
+        <f>2932+698</f>
+        <v>3630</v>
       </c>
       <c r="BC11" s="112">
         <v>4191</v>
@@ -8988,15 +8961,15 @@
         <v>46086</v>
       </c>
       <c r="BJ11" s="78">
-        <f t="shared" ref="BJ11:BJ25" si="69">+BM11/BL11</f>
+        <f t="shared" ref="BJ11:BJ25" si="68">+BM11/BL11</f>
         <v>0.64136188642925895</v>
       </c>
       <c r="BK11" s="76">
-        <f t="shared" ref="BK11:BK25" si="70">+BN11/BL11</f>
+        <f t="shared" ref="BK11:BK25" si="69">+BN11/BL11</f>
         <v>0.3586381135707411</v>
       </c>
       <c r="BL11" s="79">
-        <f t="shared" ref="BL11:BL25" si="71">BM11+BN11</f>
+        <f t="shared" ref="BL11:BL25" si="70">BM11+BN11</f>
         <v>41560</v>
       </c>
       <c r="BM11" s="155">
@@ -9017,15 +8990,9 @@
       <c r="BR11" s="157">
         <v>0.75069444444444444</v>
       </c>
-      <c r="BT11" s="14">
-        <v>7459</v>
-      </c>
-      <c r="BV11" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV11" s="175"/>
     </row>
-    <row r="12" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="56">
         <f t="shared" si="47"/>
         <v>46087</v>
@@ -9036,51 +9003,51 @@
         <v>59430</v>
       </c>
       <c r="E12" s="159">
-        <f t="shared" si="53"/>
-        <v>0.87651018004374892</v>
+        <f t="shared" si="52"/>
+        <v>0.8743732121823995</v>
       </c>
       <c r="F12" s="87">
         <f t="shared" si="24"/>
-        <v>52091</v>
+        <v>51964</v>
       </c>
       <c r="G12" s="159">
         <f>H12/D12</f>
-        <v>0.12348981995625105</v>
+        <v>0.12562678781760053</v>
       </c>
       <c r="H12" s="146">
         <f t="shared" si="26"/>
-        <v>7339</v>
+        <v>7466</v>
       </c>
       <c r="I12" s="160">
+        <f t="shared" si="54"/>
+        <v>0.11082445828314798</v>
+      </c>
+      <c r="J12" s="159">
         <f t="shared" si="55"/>
-        <v>0.11082445828314798</v>
-      </c>
-      <c r="J12" s="159">
+        <v>0.14966317237291549</v>
+      </c>
+      <c r="K12" s="159">
         <f t="shared" si="56"/>
-        <v>0.14966317237291549</v>
-      </c>
-      <c r="K12" s="159">
+        <v>0.18771273490041737</v>
+      </c>
+      <c r="L12" s="161">
         <f t="shared" si="57"/>
-        <v>0.18771273490041737</v>
-      </c>
-      <c r="L12" s="161">
+        <v>0.57460551462625997</v>
+      </c>
+      <c r="M12" s="146">
         <f t="shared" si="58"/>
-        <v>0.57460551462625997</v>
-      </c>
-      <c r="M12" s="146">
+        <v>6436.8507737726595</v>
+      </c>
+      <c r="N12" s="146">
         <f t="shared" si="59"/>
-        <v>6436.8507737726595</v>
-      </c>
-      <c r="N12" s="146">
+        <v>8692.6615461774909</v>
+      </c>
+      <c r="O12" s="146">
         <f t="shared" si="60"/>
-        <v>8692.6615461774909</v>
-      </c>
-      <c r="O12" s="146">
+        <v>10902.637212118592</v>
+      </c>
+      <c r="P12" s="146">
         <f t="shared" si="61"/>
-        <v>10902.637212118592</v>
-      </c>
-      <c r="P12" s="146">
-        <f t="shared" si="62"/>
         <v>33373.950197765116</v>
       </c>
       <c r="Q12" s="56">
@@ -9122,11 +9089,11 @@
         <v>46087</v>
       </c>
       <c r="AC12" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD12" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD12" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE12" s="163">
@@ -9156,11 +9123,11 @@
         <v>46087</v>
       </c>
       <c r="AM12" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60416349327240415</v>
+      </c>
+      <c r="AN12" s="76">
         <f t="shared" si="65"/>
-        <v>0.60416349327240415</v>
-      </c>
-      <c r="AN12" s="76">
-        <f t="shared" si="66"/>
         <v>0.39583650672759585</v>
       </c>
       <c r="AO12" s="150">
@@ -9190,12 +9157,12 @@
         <v>46087</v>
       </c>
       <c r="AW12" s="110">
+        <f t="shared" si="66"/>
+        <v>0.67116722731671352</v>
+      </c>
+      <c r="AX12" s="110">
         <f t="shared" si="67"/>
-        <v>0.68287175706188652</v>
-      </c>
-      <c r="AX12" s="110">
-        <f t="shared" si="68"/>
-        <v>0.31712824293811342</v>
+        <v>0.32883277268328648</v>
       </c>
       <c r="AY12" s="111">
         <f t="shared" si="17"/>
@@ -9206,11 +9173,11 @@
       </c>
       <c r="BA12" s="120">
         <f t="shared" si="18"/>
-        <v>7409.5</v>
+        <v>7282.5</v>
       </c>
       <c r="BB12" s="113">
-        <f>2870+571</f>
-        <v>3441</v>
+        <f>2870+698</f>
+        <v>3568</v>
       </c>
       <c r="BC12" s="112">
         <v>4308.37</v>
@@ -9235,15 +9202,15 @@
         <v>46087</v>
       </c>
       <c r="BJ12" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60467099999338758</v>
+      </c>
+      <c r="BK12" s="76">
         <f t="shared" si="69"/>
-        <v>0.60467099999338758</v>
-      </c>
-      <c r="BK12" s="76">
+        <v>0.39532900000661242</v>
+      </c>
+      <c r="BL12" s="79">
         <f t="shared" si="70"/>
-        <v>0.39532900000661242</v>
-      </c>
-      <c r="BL12" s="79">
-        <f t="shared" si="71"/>
         <v>37807.75</v>
       </c>
       <c r="BM12" s="155">
@@ -9264,15 +9231,9 @@
       <c r="BR12" s="157">
         <v>0.77638888888888891</v>
       </c>
-      <c r="BT12" s="14">
-        <v>7339</v>
-      </c>
-      <c r="BV12" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV12" s="175"/>
     </row>
-    <row r="13" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="56">
         <f t="shared" si="47"/>
         <v>46088</v>
@@ -9283,51 +9244,51 @@
         <v>35024</v>
       </c>
       <c r="E13" s="159">
-        <f t="shared" si="53"/>
-        <v>0.7930493375970763</v>
+        <f t="shared" si="52"/>
+        <v>0.78942325262677027</v>
       </c>
       <c r="F13" s="87">
         <f t="shared" si="24"/>
-        <v>27775.760000000002</v>
+        <v>27648.760000000002</v>
       </c>
       <c r="G13" s="159">
-        <f t="shared" si="54"/>
-        <v>0.2069506624029237</v>
+        <f t="shared" si="53"/>
+        <v>0.21057674737322979</v>
       </c>
       <c r="H13" s="146">
         <f t="shared" si="26"/>
-        <v>7248.24</v>
+        <v>7375.24</v>
       </c>
       <c r="I13" s="160">
+        <f t="shared" si="54"/>
+        <v>7.0365427715805409E-2</v>
+      </c>
+      <c r="J13" s="159">
         <f t="shared" si="55"/>
-        <v>7.0365427715805409E-2</v>
-      </c>
-      <c r="J13" s="159">
+        <v>0.14817605404473505</v>
+      </c>
+      <c r="K13" s="159">
         <f t="shared" si="56"/>
-        <v>0.14817605404473505</v>
-      </c>
-      <c r="K13" s="159">
+        <v>0.16247777039300532</v>
+      </c>
+      <c r="L13" s="161">
         <f t="shared" si="57"/>
-        <v>0.16247777039300532</v>
-      </c>
-      <c r="L13" s="161">
+        <v>0.65514555171731237</v>
+      </c>
+      <c r="M13" s="146">
         <f t="shared" si="58"/>
-        <v>0.65514555171731237</v>
-      </c>
-      <c r="M13" s="146">
+        <v>2373.9184348481272</v>
+      </c>
+      <c r="N13" s="146">
         <f t="shared" si="59"/>
-        <v>2373.9184348481272</v>
-      </c>
-      <c r="N13" s="146">
+        <v>4999.0155353072259</v>
+      </c>
+      <c r="O13" s="146">
         <f t="shared" si="60"/>
-        <v>4999.0155353072259</v>
-      </c>
-      <c r="O13" s="146">
+        <v>5481.51253974882</v>
+      </c>
+      <c r="P13" s="146">
         <f t="shared" si="61"/>
-        <v>5481.51253974882</v>
-      </c>
-      <c r="P13" s="146">
-        <f t="shared" si="62"/>
         <v>22102.645478286966</v>
       </c>
       <c r="Q13" s="56">
@@ -9369,11 +9330,11 @@
         <v>46088</v>
       </c>
       <c r="AC13" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD13" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD13" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE13" s="163">
@@ -9403,11 +9364,11 @@
         <v>46088</v>
       </c>
       <c r="AM13" s="77">
+        <f t="shared" si="64"/>
+        <v>0.34581746100146515</v>
+      </c>
+      <c r="AN13" s="76">
         <f t="shared" si="65"/>
-        <v>0.34581746100146515</v>
-      </c>
-      <c r="AN13" s="76">
-        <f t="shared" si="66"/>
         <v>0.65418253899853485</v>
       </c>
       <c r="AO13" s="150">
@@ -9437,12 +9398,12 @@
         <v>46088</v>
       </c>
       <c r="AW13" s="169">
+        <f t="shared" si="66"/>
+        <v>0.27610959458093215</v>
+      </c>
+      <c r="AX13" s="169">
         <f t="shared" si="67"/>
-        <v>0.30178950561116163</v>
-      </c>
-      <c r="AX13" s="169">
-        <f t="shared" si="68"/>
-        <v>0.69821049438883831</v>
+        <v>0.7238904054190678</v>
       </c>
       <c r="AY13" s="111">
         <f t="shared" si="17"/>
@@ -9453,11 +9414,11 @@
       </c>
       <c r="BA13" s="120">
         <f t="shared" si="18"/>
-        <v>1492.5</v>
+        <v>1365.5</v>
       </c>
       <c r="BB13" s="113">
-        <f>2882+571</f>
-        <v>3453</v>
+        <f>2882+698</f>
+        <v>3580</v>
       </c>
       <c r="BC13" s="112">
         <v>1521.62</v>
@@ -9482,15 +9443,15 @@
         <v>46088</v>
       </c>
       <c r="BJ13" s="170">
+        <f t="shared" si="68"/>
+        <v>0.61541085543307705</v>
+      </c>
+      <c r="BK13" s="76">
         <f t="shared" si="69"/>
-        <v>0.61541085543307705</v>
-      </c>
-      <c r="BK13" s="76">
+        <v>0.384589144566923</v>
+      </c>
+      <c r="BL13" s="79">
         <f t="shared" si="70"/>
-        <v>0.384589144566923</v>
-      </c>
-      <c r="BL13" s="79">
-        <f t="shared" si="71"/>
         <v>25650.75</v>
       </c>
       <c r="BM13" s="155">
@@ -9511,15 +9472,9 @@
       <c r="BR13" s="157">
         <v>0.37013888888888891</v>
       </c>
-      <c r="BT13" s="14">
-        <v>7248.24</v>
-      </c>
-      <c r="BV13" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV13" s="175"/>
     </row>
-    <row r="14" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="56">
         <f t="shared" si="47"/>
         <v>46089</v>
@@ -9530,52 +9485,52 @@
         <v>32942</v>
       </c>
       <c r="E14" s="159">
-        <f t="shared" si="53"/>
-        <v>0.78058405682715071</v>
+        <f t="shared" si="52"/>
+        <v>0.77672879606581269</v>
       </c>
       <c r="F14" s="87">
         <f t="shared" si="24"/>
-        <v>25714</v>
+        <v>25587</v>
       </c>
       <c r="G14" s="159">
-        <f t="shared" si="54"/>
-        <v>0.21941594317284924</v>
+        <f t="shared" si="53"/>
+        <v>0.22327120393418737</v>
       </c>
       <c r="H14" s="146">
         <f t="shared" si="26"/>
-        <v>7228</v>
+        <v>7355</v>
       </c>
       <c r="I14" s="160">
+        <f t="shared" si="54"/>
+        <v>5.9761984665823373E-2</v>
+      </c>
+      <c r="J14" s="159">
         <f t="shared" si="55"/>
-        <v>5.9958559958559955E-2</v>
-      </c>
-      <c r="J14" s="159">
+        <v>0.14337713297364277</v>
+      </c>
+      <c r="K14" s="159">
         <f t="shared" si="56"/>
-        <v>0.14384874384874385</v>
-      </c>
-      <c r="K14" s="159">
+        <v>0.20553641808645998</v>
+      </c>
+      <c r="L14" s="161">
         <f t="shared" si="57"/>
-        <v>0.20239282153539381</v>
-      </c>
-      <c r="L14" s="161">
+        <v>0.62588739448072905</v>
+      </c>
+      <c r="M14" s="146">
         <f t="shared" si="58"/>
-        <v>0.62794612794612792</v>
-      </c>
-      <c r="M14" s="146">
+        <v>1887.2237137620364</v>
+      </c>
+      <c r="N14" s="146">
         <f t="shared" si="59"/>
-        <v>1893.4313649313649</v>
-      </c>
-      <c r="N14" s="146">
+        <v>4527.7064821746653</v>
+      </c>
+      <c r="O14" s="146">
         <f t="shared" si="60"/>
-        <v>4542.5994819994821</v>
-      </c>
-      <c r="O14" s="146">
+        <v>6490.6345467523197</v>
+      </c>
+      <c r="P14" s="146">
         <f t="shared" si="61"/>
-        <v>6391.3629112662011</v>
-      </c>
-      <c r="P14" s="146">
-        <f t="shared" si="62"/>
-        <v>19829.910774410775</v>
+        <v>19764.898030306944</v>
       </c>
       <c r="Q14" s="56">
         <f t="shared" si="48"/>
@@ -9616,18 +9571,18 @@
         <v>46089</v>
       </c>
       <c r="AC14" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD14" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD14" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE14" s="163">
         <v>2315</v>
       </c>
       <c r="AF14" s="118">
-        <f t="shared" ref="AF14" si="72">+AE14-AG14</f>
+        <f t="shared" ref="AF14" si="71">+AE14-AG14</f>
         <v>2315</v>
       </c>
       <c r="AG14" s="147">
@@ -9650,18 +9605,18 @@
         <v>46089</v>
       </c>
       <c r="AM14" s="77">
+        <f t="shared" si="64"/>
+        <v>0.33471371984155562</v>
+      </c>
+      <c r="AN14" s="76">
         <f t="shared" si="65"/>
-        <v>0.33471371984155562</v>
-      </c>
-      <c r="AN14" s="76">
-        <f t="shared" si="66"/>
         <v>0.66528628015844438</v>
       </c>
       <c r="AO14" s="150">
         <v>5554</v>
       </c>
       <c r="AP14" s="117">
-        <f t="shared" ref="AP14" si="73">AO14-AQ14</f>
+        <f t="shared" ref="AP14" si="72">AO14-AQ14</f>
         <v>1859</v>
       </c>
       <c r="AQ14" s="151">
@@ -9684,16 +9639,16 @@
         <v>46089</v>
       </c>
       <c r="AW14" s="110">
+        <f t="shared" si="66"/>
+        <v>0.58487958941966045</v>
+      </c>
+      <c r="AX14" s="110">
         <f t="shared" si="67"/>
-        <v>0.58487958941966045</v>
-      </c>
-      <c r="AX14" s="110">
-        <f t="shared" si="68"/>
-        <v>0.69739439399921044</v>
+        <v>0.72246348203711019</v>
       </c>
       <c r="AY14" s="111">
         <f t="shared" si="17"/>
-        <v>6496</v>
+        <v>6623</v>
       </c>
       <c r="AZ14" s="112">
         <v>5066</v>
@@ -9702,8 +9657,8 @@
         <v>2963</v>
       </c>
       <c r="BB14" s="113">
-        <f>2962+571</f>
-        <v>3533</v>
+        <f>2962+698</f>
+        <v>3660</v>
       </c>
       <c r="BC14" s="112">
         <v>2880</v>
@@ -9728,15 +9683,15 @@
         <v>46089</v>
       </c>
       <c r="BJ14" s="78">
+        <f t="shared" si="68"/>
+        <v>0.67477830480511447</v>
+      </c>
+      <c r="BK14" s="76">
         <f t="shared" si="69"/>
-        <v>0.67477830480511447</v>
-      </c>
-      <c r="BK14" s="76">
+        <v>0.32522169519488553</v>
+      </c>
+      <c r="BL14" s="79">
         <f t="shared" si="70"/>
-        <v>0.32522169519488553</v>
-      </c>
-      <c r="BL14" s="79">
-        <f t="shared" si="71"/>
         <v>24245</v>
       </c>
       <c r="BM14" s="155">
@@ -9757,15 +9712,9 @@
       <c r="BR14" s="157">
         <v>0.98958333333333337</v>
       </c>
-      <c r="BT14" s="14">
-        <v>7228</v>
-      </c>
-      <c r="BV14" s="175">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
+      <c r="BV14" s="175"/>
     </row>
-    <row r="15" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="56">
         <f t="shared" si="47"/>
         <v>46090</v>
@@ -9776,51 +9725,51 @@
         <v>54500</v>
       </c>
       <c r="E15" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86071559633027528</v>
+        <f t="shared" si="52"/>
+        <v>0.85838532110091748</v>
       </c>
       <c r="F15" s="87">
         <f t="shared" si="24"/>
-        <v>46909</v>
+        <v>46782</v>
       </c>
       <c r="G15" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13928440366972478</v>
+        <f t="shared" si="53"/>
+        <v>0.14161467889908258</v>
       </c>
       <c r="H15" s="146">
         <f t="shared" si="26"/>
-        <v>7591</v>
+        <v>7718</v>
       </c>
       <c r="I15" s="160">
+        <f t="shared" si="54"/>
+        <v>0.11671066314694824</v>
+      </c>
+      <c r="J15" s="159">
         <f t="shared" si="55"/>
-        <v>0.11671066314694824</v>
-      </c>
-      <c r="J15" s="159">
+        <v>0.15822734181265499</v>
+      </c>
+      <c r="K15" s="159">
         <f t="shared" si="56"/>
-        <v>0.15822734181265499</v>
-      </c>
-      <c r="K15" s="159">
+        <v>0.17075674162545487</v>
+      </c>
+      <c r="L15" s="161">
         <f t="shared" si="57"/>
-        <v>0.17075674162545487</v>
-      </c>
-      <c r="L15" s="161">
+        <v>0.57867370610351176</v>
+      </c>
+      <c r="M15" s="146">
         <f t="shared" si="58"/>
-        <v>0.57867370610351176</v>
-      </c>
-      <c r="M15" s="146">
+        <v>6331.553475721942</v>
+      </c>
+      <c r="N15" s="146">
         <f t="shared" si="59"/>
-        <v>6331.553475721942</v>
-      </c>
-      <c r="N15" s="146">
+        <v>8583.8332933365327</v>
+      </c>
+      <c r="O15" s="146">
         <f t="shared" si="60"/>
-        <v>8583.8332933365327</v>
-      </c>
-      <c r="O15" s="146">
+        <v>9263.5532331809263</v>
+      </c>
+      <c r="P15" s="146">
         <f t="shared" si="61"/>
-        <v>9263.5532331809263</v>
-      </c>
-      <c r="P15" s="146">
-        <f t="shared" si="62"/>
         <v>31393.048556115515</v>
       </c>
       <c r="Q15" s="56">
@@ -9862,11 +9811,11 @@
         <v>46090</v>
       </c>
       <c r="AC15" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD15" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE15" s="163">
@@ -9896,11 +9845,11 @@
         <v>46090</v>
       </c>
       <c r="AM15" s="77">
+        <f t="shared" si="64"/>
+        <v>0.59049544994944392</v>
+      </c>
+      <c r="AN15" s="76">
         <f t="shared" si="65"/>
-        <v>0.59049544994944392</v>
-      </c>
-      <c r="AN15" s="76">
-        <f t="shared" si="66"/>
         <v>0.40950455005055614</v>
       </c>
       <c r="AO15" s="150">
@@ -9930,12 +9879,12 @@
         <v>46090</v>
       </c>
       <c r="AW15" s="169">
+        <f t="shared" si="66"/>
+        <v>0.59912568306010927</v>
+      </c>
+      <c r="AX15" s="169">
         <f t="shared" si="67"/>
-        <v>0.61300546448087434</v>
-      </c>
-      <c r="AX15" s="169">
-        <f t="shared" si="68"/>
-        <v>0.38699453551912566</v>
+        <v>0.40087431693989073</v>
       </c>
       <c r="AY15" s="111">
         <f t="shared" si="17"/>
@@ -9946,11 +9895,11 @@
       </c>
       <c r="BA15" s="120">
         <f t="shared" si="18"/>
-        <v>5609</v>
+        <v>5482</v>
       </c>
       <c r="BB15" s="113">
-        <f>2970+571</f>
-        <v>3541</v>
+        <f>2970+698</f>
+        <v>3668</v>
       </c>
       <c r="BC15" s="112">
         <v>4190</v>
@@ -9975,15 +9924,15 @@
         <v>46090</v>
       </c>
       <c r="BJ15" s="170">
+        <f t="shared" si="68"/>
+        <v>0.6123859552115013</v>
+      </c>
+      <c r="BK15" s="76">
         <f t="shared" si="69"/>
-        <v>0.6123859552115013</v>
-      </c>
-      <c r="BK15" s="76">
+        <v>0.38761404478849876</v>
+      </c>
+      <c r="BL15" s="79">
         <f t="shared" si="70"/>
-        <v>0.38761404478849876</v>
-      </c>
-      <c r="BL15" s="79">
-        <f t="shared" si="71"/>
         <v>36170</v>
       </c>
       <c r="BM15" s="155">
@@ -10004,15 +9953,9 @@
       <c r="BR15" s="157">
         <v>0.875</v>
       </c>
-      <c r="BT15" s="14">
-        <v>7530</v>
-      </c>
-      <c r="BV15" s="175">
-        <f t="shared" si="52"/>
-        <v>-61</v>
-      </c>
+      <c r="BV15" s="175"/>
     </row>
-    <row r="16" spans="1:75" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="56">
         <f t="shared" si="47"/>
         <v>46091</v>
@@ -10023,51 +9966,51 @@
         <v>55200</v>
       </c>
       <c r="E16" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86067028985507243</v>
+        <f t="shared" si="52"/>
+        <v>0.85836956521739127</v>
       </c>
       <c r="F16" s="87">
         <f t="shared" si="24"/>
-        <v>47509</v>
+        <v>47382</v>
       </c>
       <c r="G16" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13932971014492754</v>
+        <f t="shared" si="53"/>
+        <v>0.1416304347826087</v>
       </c>
       <c r="H16" s="146">
         <f t="shared" si="26"/>
-        <v>7691</v>
+        <v>7818</v>
       </c>
       <c r="I16" s="160">
+        <f t="shared" si="54"/>
+        <v>0.11760961247712262</v>
+      </c>
+      <c r="J16" s="159">
         <f t="shared" si="55"/>
-        <v>0.11760961247712262</v>
-      </c>
-      <c r="J16" s="159">
+        <v>0.15922654571496778</v>
+      </c>
+      <c r="K16" s="159">
         <f t="shared" si="56"/>
-        <v>0.15922654571496778</v>
-      </c>
-      <c r="K16" s="159">
+        <v>0.17027202673846439</v>
+      </c>
+      <c r="L16" s="161">
         <f t="shared" si="57"/>
-        <v>0.17027202673846439</v>
-      </c>
-      <c r="L16" s="161">
+        <v>0.5772260682740511</v>
+      </c>
+      <c r="M16" s="146">
         <f t="shared" si="58"/>
-        <v>0.5772260682740511</v>
-      </c>
-      <c r="M16" s="146">
+        <v>6380.3214768839025</v>
+      </c>
+      <c r="N16" s="146">
         <f t="shared" si="59"/>
-        <v>6380.3214768839025</v>
-      </c>
-      <c r="N16" s="146">
+        <v>8638.0401050370019</v>
+      </c>
+      <c r="O16" s="146">
         <f t="shared" si="60"/>
-        <v>8638.0401050370019</v>
-      </c>
-      <c r="O16" s="146">
+        <v>9237.257450561694</v>
+      </c>
+      <c r="P16" s="146">
         <f t="shared" si="61"/>
-        <v>9237.257450561694</v>
-      </c>
-      <c r="P16" s="146">
-        <f t="shared" si="62"/>
         <v>31314.514203867271</v>
       </c>
       <c r="Q16" s="56">
@@ -10109,11 +10052,11 @@
         <v>46091</v>
       </c>
       <c r="AC16" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD16" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD16" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE16" s="163">
@@ -10143,11 +10086,11 @@
         <v>46091</v>
       </c>
       <c r="AM16" s="77">
+        <f t="shared" si="64"/>
+        <v>0.59020489755122441</v>
+      </c>
+      <c r="AN16" s="76">
         <f t="shared" si="65"/>
-        <v>0.59020489755122441</v>
-      </c>
-      <c r="AN16" s="76">
-        <f t="shared" si="66"/>
         <v>0.40979510244877559</v>
       </c>
       <c r="AO16" s="150">
@@ -10177,12 +10120,12 @@
         <v>46091</v>
       </c>
       <c r="AW16" s="110">
+        <f t="shared" si="66"/>
+        <v>0.59454743729552895</v>
+      </c>
+      <c r="AX16" s="110">
         <f t="shared" si="67"/>
-        <v>0.60839694656488552</v>
-      </c>
-      <c r="AX16" s="110">
-        <f t="shared" si="68"/>
-        <v>0.39160305343511448</v>
+        <v>0.40545256270447111</v>
       </c>
       <c r="AY16" s="111">
         <f t="shared" si="17"/>
@@ -10193,11 +10136,11 @@
       </c>
       <c r="BA16" s="120">
         <f t="shared" si="18"/>
-        <v>5579</v>
+        <v>5452</v>
       </c>
       <c r="BB16" s="113">
-        <f>3020+571</f>
-        <v>3591</v>
+        <f>3020+698</f>
+        <v>3718</v>
       </c>
       <c r="BC16" s="112">
         <v>4200</v>
@@ -10222,15 +10165,15 @@
         <v>46091</v>
       </c>
       <c r="BJ16" s="78">
+        <f t="shared" si="68"/>
+        <v>0.61262751585332231</v>
+      </c>
+      <c r="BK16" s="76">
         <f t="shared" si="69"/>
-        <v>0.61262751585332231</v>
-      </c>
-      <c r="BK16" s="76">
+        <v>0.38737248414667769</v>
+      </c>
+      <c r="BL16" s="79">
         <f t="shared" si="70"/>
-        <v>0.38737248414667769</v>
-      </c>
-      <c r="BL16" s="79">
-        <f t="shared" si="71"/>
         <v>36270</v>
       </c>
       <c r="BM16" s="155">
@@ -10251,13 +10194,7 @@
       <c r="BR16" s="157">
         <v>0.85416666666666663</v>
       </c>
-      <c r="BT16" s="14">
-        <v>7620</v>
-      </c>
-      <c r="BV16" s="175">
-        <f t="shared" si="52"/>
-        <v>-71</v>
-      </c>
+      <c r="BV16" s="175"/>
     </row>
     <row r="17" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="56">
@@ -10270,51 +10207,51 @@
         <v>57878</v>
       </c>
       <c r="E17" s="159">
-        <f t="shared" si="53"/>
-        <v>0.8663568195169149</v>
+        <f t="shared" si="52"/>
+        <v>0.864162548809565</v>
       </c>
       <c r="F17" s="87">
         <f t="shared" si="24"/>
-        <v>50143</v>
+        <v>50016</v>
       </c>
       <c r="G17" s="159">
-        <f t="shared" si="54"/>
-        <v>0.1336431804830851</v>
+        <f t="shared" si="53"/>
+        <v>0.13583745119043505</v>
       </c>
       <c r="H17" s="146">
         <f t="shared" si="26"/>
-        <v>7735</v>
+        <v>7862</v>
       </c>
       <c r="I17" s="160">
+        <f t="shared" si="54"/>
+        <v>0.1178039044470779</v>
+      </c>
+      <c r="J17" s="159">
         <f t="shared" si="55"/>
-        <v>0.1178039044470779</v>
-      </c>
-      <c r="J17" s="159">
+        <v>0.15943678662758062</v>
+      </c>
+      <c r="K17" s="159">
         <f t="shared" si="56"/>
-        <v>0.15943678662758062</v>
-      </c>
-      <c r="K17" s="159">
+        <v>0.18790275595416747</v>
+      </c>
+      <c r="L17" s="161">
         <f t="shared" si="57"/>
-        <v>0.18790275595416747</v>
-      </c>
-      <c r="L17" s="161">
+        <v>0.55680471527474584</v>
+      </c>
+      <c r="M17" s="146">
         <f t="shared" si="58"/>
-        <v>0.55680471527474584</v>
-      </c>
-      <c r="M17" s="146">
+        <v>6670.0570697935509</v>
+      </c>
+      <c r="N17" s="146">
         <f t="shared" si="59"/>
-        <v>6670.0570697935509</v>
-      </c>
-      <c r="N17" s="146">
+        <v>9027.3108588536143</v>
+      </c>
+      <c r="O17" s="146">
         <f t="shared" si="60"/>
-        <v>9027.3108588536143</v>
-      </c>
-      <c r="O17" s="146">
+        <v>10639.054042124963</v>
+      </c>
+      <c r="P17" s="146">
         <f t="shared" si="61"/>
-        <v>10639.054042124963</v>
-      </c>
-      <c r="P17" s="146">
-        <f t="shared" si="62"/>
         <v>31526.28297885611</v>
       </c>
       <c r="Q17" s="56">
@@ -10356,11 +10293,11 @@
         <v>46092</v>
       </c>
       <c r="AC17" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD17" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD17" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE17" s="163">
@@ -10390,11 +10327,11 @@
         <v>46092</v>
       </c>
       <c r="AM17" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60176039119804403</v>
+      </c>
+      <c r="AN17" s="76">
         <f t="shared" si="65"/>
-        <v>0.60176039119804403</v>
-      </c>
-      <c r="AN17" s="76">
-        <f t="shared" si="66"/>
         <v>0.39823960880195597</v>
       </c>
       <c r="AO17" s="150">
@@ -10424,12 +10361,12 @@
         <v>46092</v>
       </c>
       <c r="AW17" s="110">
+        <f t="shared" si="66"/>
+        <v>0.6438973973503711</v>
+      </c>
+      <c r="AX17" s="110">
         <f t="shared" si="67"/>
-        <v>0.65583012308559618</v>
-      </c>
-      <c r="AX17" s="110">
-        <f t="shared" si="68"/>
-        <v>0.34416987691440382</v>
+        <v>0.35610260264962884</v>
       </c>
       <c r="AY17" s="111">
         <f t="shared" si="17"/>
@@ -10440,11 +10377,11 @@
       </c>
       <c r="BA17" s="120">
         <f t="shared" si="18"/>
-        <v>6980</v>
+        <v>6853</v>
       </c>
       <c r="BB17" s="113">
-        <f>3092+571</f>
-        <v>3663</v>
+        <f>3092+698</f>
+        <v>3790</v>
       </c>
       <c r="BC17" s="112">
         <v>5132</v>
@@ -10469,15 +10406,15 @@
         <v>46092</v>
       </c>
       <c r="BJ17" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60620571844633009</v>
+      </c>
+      <c r="BK17" s="76">
         <f t="shared" si="69"/>
-        <v>0.60620571844633009</v>
-      </c>
-      <c r="BK17" s="76">
+        <v>0.39379428155366997</v>
+      </c>
+      <c r="BL17" s="79">
         <f t="shared" si="70"/>
-        <v>0.39379428155366997</v>
-      </c>
-      <c r="BL17" s="79">
-        <f t="shared" si="71"/>
         <v>35709</v>
       </c>
       <c r="BM17" s="155">
@@ -10498,13 +10435,7 @@
       <c r="BR17" s="157">
         <v>0.76041666666666663</v>
       </c>
-      <c r="BT17" s="14">
-        <v>7685</v>
-      </c>
-      <c r="BV17" s="175">
-        <f t="shared" si="52"/>
-        <v>-50</v>
-      </c>
+      <c r="BV17" s="175"/>
     </row>
     <row r="18" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="56">
@@ -10517,51 +10448,51 @@
         <v>58406</v>
       </c>
       <c r="E18" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86741088244358455</v>
+        <f t="shared" si="52"/>
+        <v>0.86523644831010516</v>
       </c>
       <c r="F18" s="87">
         <f t="shared" si="24"/>
-        <v>50662</v>
+        <v>50535</v>
       </c>
       <c r="G18" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13258911755641545</v>
+        <f t="shared" si="53"/>
+        <v>0.13476355168989487</v>
       </c>
       <c r="H18" s="146">
         <f t="shared" si="26"/>
-        <v>7744</v>
+        <v>7871</v>
       </c>
       <c r="I18" s="160">
+        <f t="shared" si="54"/>
+        <v>0.11895139437295799</v>
+      </c>
+      <c r="J18" s="159">
         <f t="shared" si="55"/>
-        <v>0.11895139437295799</v>
-      </c>
-      <c r="J18" s="159">
+        <v>0.15956705532586984</v>
+      </c>
+      <c r="K18" s="159">
         <f t="shared" si="56"/>
-        <v>0.15956705532586984</v>
-      </c>
-      <c r="K18" s="159">
+        <v>0.17182229757760503</v>
+      </c>
+      <c r="L18" s="161">
         <f t="shared" si="57"/>
-        <v>0.17182229757760503</v>
-      </c>
-      <c r="L18" s="161">
+        <v>0.57397686626097455</v>
+      </c>
+      <c r="M18" s="146">
         <f t="shared" si="58"/>
-        <v>0.57397686626097455</v>
-      </c>
-      <c r="M18" s="146">
+        <v>6794.0278410058681</v>
+      </c>
+      <c r="N18" s="146">
         <f t="shared" si="59"/>
-        <v>6794.0278410058681</v>
-      </c>
-      <c r="N18" s="146">
+        <v>9113.8319319923812</v>
+      </c>
+      <c r="O18" s="146">
         <f t="shared" si="60"/>
-        <v>9113.8319319923812</v>
-      </c>
-      <c r="O18" s="146">
+        <v>9813.8023484424884</v>
+      </c>
+      <c r="P18" s="146">
         <f t="shared" si="61"/>
-        <v>9813.8023484424884</v>
-      </c>
-      <c r="P18" s="146">
-        <f t="shared" si="62"/>
         <v>32783.262693361823</v>
       </c>
       <c r="Q18" s="56">
@@ -10603,11 +10534,11 @@
         <v>46093</v>
       </c>
       <c r="AC18" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD18" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD18" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE18" s="163">
@@ -10637,11 +10568,11 @@
         <v>46093</v>
       </c>
       <c r="AM18" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60465793304221249</v>
+      </c>
+      <c r="AN18" s="76">
         <f t="shared" si="65"/>
-        <v>0.60465793304221249</v>
-      </c>
-      <c r="AN18" s="76">
-        <f t="shared" si="66"/>
         <v>0.39534206695778751</v>
       </c>
       <c r="AO18" s="150">
@@ -10671,12 +10602,12 @@
         <v>46093</v>
       </c>
       <c r="AW18" s="110">
+        <f t="shared" si="66"/>
+        <v>0.60140667646441315</v>
+      </c>
+      <c r="AX18" s="110">
         <f t="shared" si="67"/>
-        <v>0.61473861011967246</v>
-      </c>
-      <c r="AX18" s="110">
-        <f t="shared" si="68"/>
-        <v>0.38526138988032754</v>
+        <v>0.3985933235355868</v>
       </c>
       <c r="AY18" s="111">
         <f t="shared" si="17"/>
@@ -10687,11 +10618,11 @@
       </c>
       <c r="BA18" s="120">
         <f t="shared" si="18"/>
-        <v>5856</v>
+        <v>5729</v>
       </c>
       <c r="BB18" s="113">
-        <f>3099+571</f>
-        <v>3670</v>
+        <f>3099+698</f>
+        <v>3797</v>
       </c>
       <c r="BC18" s="112">
         <v>3739</v>
@@ -10716,15 +10647,15 @@
         <v>46093</v>
       </c>
       <c r="BJ18" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60634509550016191</v>
+      </c>
+      <c r="BK18" s="76">
         <f t="shared" si="69"/>
-        <v>0.60634509550016191</v>
-      </c>
-      <c r="BK18" s="76">
+        <v>0.39365490449983814</v>
+      </c>
+      <c r="BL18" s="79">
         <f t="shared" si="70"/>
-        <v>0.39365490449983814</v>
-      </c>
-      <c r="BL18" s="79">
-        <f t="shared" si="71"/>
         <v>37068</v>
       </c>
       <c r="BM18" s="155">
@@ -10745,13 +10676,7 @@
       <c r="BR18" s="157">
         <v>0.75208333333333333</v>
       </c>
-      <c r="BT18" s="14">
-        <v>7694</v>
-      </c>
-      <c r="BV18" s="175">
-        <f t="shared" si="52"/>
-        <v>-50</v>
-      </c>
+      <c r="BV18" s="175"/>
     </row>
     <row r="19" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="56">
@@ -10764,51 +10689,51 @@
         <v>55700</v>
       </c>
       <c r="E19" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86518850987432672</v>
+        <f t="shared" si="52"/>
+        <v>0.86290843806104134</v>
       </c>
       <c r="F19" s="87">
         <f t="shared" si="24"/>
-        <v>48191</v>
+        <v>48064</v>
       </c>
       <c r="G19" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13481149012567326</v>
+        <f t="shared" si="53"/>
+        <v>0.13709156193895872</v>
       </c>
       <c r="H19" s="146">
         <f t="shared" si="26"/>
-        <v>7509</v>
+        <v>7636</v>
       </c>
       <c r="I19" s="160">
+        <f t="shared" si="54"/>
+        <v>0.1217030957991387</v>
+      </c>
+      <c r="J19" s="159">
         <f t="shared" si="55"/>
-        <v>0.1217030957991387</v>
-      </c>
-      <c r="J19" s="159">
+        <v>0.16039652230437962</v>
+      </c>
+      <c r="K19" s="159">
         <f t="shared" si="56"/>
-        <v>0.16039652230437962</v>
-      </c>
-      <c r="K19" s="159">
+        <v>0.17108255628837843</v>
+      </c>
+      <c r="L19" s="161">
         <f t="shared" si="57"/>
-        <v>0.17108255628837843</v>
-      </c>
-      <c r="L19" s="161">
+        <v>0.57120338019013572</v>
+      </c>
+      <c r="M19" s="146">
         <f t="shared" si="58"/>
-        <v>0.57120338019013572</v>
-      </c>
-      <c r="M19" s="146">
+        <v>6624.7863167303158</v>
+      </c>
+      <c r="N19" s="146">
         <f t="shared" si="59"/>
-        <v>6624.7863167303158</v>
-      </c>
-      <c r="N19" s="146">
+        <v>8731.0242951166001</v>
+      </c>
+      <c r="O19" s="146">
         <f t="shared" si="60"/>
-        <v>8731.0242951166001</v>
-      </c>
-      <c r="O19" s="146">
+        <v>9312.7078690015915</v>
+      </c>
+      <c r="P19" s="146">
         <f t="shared" si="61"/>
-        <v>9312.7078690015915</v>
-      </c>
-      <c r="P19" s="146">
-        <f t="shared" si="62"/>
         <v>31092.88479726985</v>
       </c>
       <c r="Q19" s="56">
@@ -10850,11 +10775,11 @@
         <v>46094</v>
       </c>
       <c r="AC19" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD19" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD19" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE19" s="163">
@@ -10884,11 +10809,11 @@
         <v>46094</v>
       </c>
       <c r="AM19" s="77">
-        <f t="shared" ref="AM19" si="74">+AP19/AO19</f>
+        <f t="shared" ref="AM19" si="73">+AP19/AO19</f>
         <v>0.59635258358662613</v>
       </c>
       <c r="AN19" s="76">
-        <f t="shared" ref="AN19" si="75">+AQ19/AO19</f>
+        <f t="shared" ref="AN19" si="74">+AQ19/AO19</f>
         <v>0.40364741641337387</v>
       </c>
       <c r="AO19" s="150">
@@ -10918,12 +10843,12 @@
         <v>46094</v>
       </c>
       <c r="AW19" s="110">
-        <f t="shared" ref="AW19" si="76">BA19/AZ19</f>
-        <v>0.60950481887670327</v>
+        <f t="shared" ref="AW19" si="75">BA19/AZ19</f>
+        <v>0.59543591447878585</v>
       </c>
       <c r="AX19" s="110">
-        <f t="shared" ref="AX19" si="77">BB19/AZ19</f>
-        <v>0.39049518112329679</v>
+        <f t="shared" ref="AX19" si="76">BB19/AZ19</f>
+        <v>0.40456408552121415</v>
       </c>
       <c r="AY19" s="111">
         <f t="shared" si="17"/>
@@ -10934,11 +10859,11 @@
       </c>
       <c r="BA19" s="120">
         <f t="shared" si="18"/>
-        <v>5502</v>
+        <v>5375</v>
       </c>
       <c r="BB19" s="113">
-        <f>2954+571</f>
-        <v>3525</v>
+        <f>2954+698</f>
+        <v>3652</v>
       </c>
       <c r="BC19" s="181">
         <v>4460</v>
@@ -10963,15 +10888,15 @@
         <v>46094</v>
       </c>
       <c r="BJ19" s="78">
-        <f t="shared" ref="BJ19" si="78">+BM19/BL19</f>
+        <f t="shared" ref="BJ19" si="77">+BM19/BL19</f>
         <v>0.60698739651199185</v>
       </c>
       <c r="BK19" s="76">
-        <f t="shared" ref="BK19" si="79">+BN19/BL19</f>
+        <f t="shared" ref="BK19" si="78">+BN19/BL19</f>
         <v>0.39301260348800821</v>
       </c>
       <c r="BL19" s="79">
-        <f t="shared" ref="BL19" si="80">BM19+BN19</f>
+        <f t="shared" ref="BL19" si="79">BM19+BN19</f>
         <v>35149</v>
       </c>
       <c r="BM19" s="155">
@@ -10992,13 +10917,7 @@
       <c r="BR19" s="157">
         <v>0.80277777777777781</v>
       </c>
-      <c r="BT19" s="14">
-        <v>7459</v>
-      </c>
-      <c r="BV19" s="175">
-        <f t="shared" si="52"/>
-        <v>-50</v>
-      </c>
+      <c r="BV19" s="175"/>
     </row>
     <row r="20" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="56">
@@ -11011,7 +10930,7 @@
         <v>33634</v>
       </c>
       <c r="E20" s="159">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0.80475114467503117</v>
       </c>
       <c r="F20" s="87">
@@ -11019,7 +10938,7 @@
         <v>27067</v>
       </c>
       <c r="G20" s="159">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0.19524885532496877</v>
       </c>
       <c r="H20" s="146">
@@ -11027,35 +10946,35 @@
         <v>6567</v>
       </c>
       <c r="I20" s="160">
+        <f t="shared" si="54"/>
+        <v>8.0070697873707894E-2</v>
+      </c>
+      <c r="J20" s="159">
         <f t="shared" si="55"/>
-        <v>8.0070697873707894E-2</v>
-      </c>
-      <c r="J20" s="159">
+        <v>0.12958598896684698</v>
+      </c>
+      <c r="K20" s="159">
         <f t="shared" si="56"/>
-        <v>0.12958598896684698</v>
-      </c>
-      <c r="K20" s="159">
+        <v>0.18769349845201239</v>
+      </c>
+      <c r="L20" s="161">
         <f t="shared" si="57"/>
-        <v>0.18769349845201239</v>
-      </c>
-      <c r="L20" s="161">
+        <v>0.6344866370306893</v>
+      </c>
+      <c r="M20" s="146">
         <f t="shared" si="58"/>
-        <v>0.6344866370306893</v>
-      </c>
-      <c r="M20" s="146">
+        <v>2579.7177440951209</v>
+      </c>
+      <c r="N20" s="146">
         <f t="shared" si="59"/>
-        <v>2579.7177440951209</v>
-      </c>
-      <c r="N20" s="146">
+        <v>4175.0013925338762</v>
+      </c>
+      <c r="O20" s="146">
         <f t="shared" si="60"/>
-        <v>4175.0013925338762</v>
-      </c>
-      <c r="O20" s="146">
+        <v>6047.1091331269354</v>
+      </c>
+      <c r="P20" s="146">
         <f t="shared" si="61"/>
-        <v>6047.1091331269354</v>
-      </c>
-      <c r="P20" s="146">
-        <f t="shared" si="62"/>
         <v>20441.890471854749</v>
       </c>
       <c r="Q20" s="56">
@@ -11097,11 +11016,11 @@
         <v>46095</v>
       </c>
       <c r="AC20" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD20" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD20" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE20" s="163">
@@ -11131,11 +11050,11 @@
         <v>46095</v>
       </c>
       <c r="AM20" s="77">
+        <f t="shared" si="64"/>
+        <v>0.41620169456499279</v>
+      </c>
+      <c r="AN20" s="76">
         <f t="shared" si="65"/>
-        <v>0.41620169456499279</v>
-      </c>
-      <c r="AN20" s="76">
-        <f t="shared" si="66"/>
         <v>0.58379830543500721</v>
       </c>
       <c r="AO20" s="150">
@@ -11165,11 +11084,11 @@
         <v>46095</v>
       </c>
       <c r="AW20" s="110">
+        <f t="shared" si="66"/>
+        <v>0.35704467353951891</v>
+      </c>
+      <c r="AX20" s="110">
         <f t="shared" si="67"/>
-        <v>0.35704467353951891</v>
-      </c>
-      <c r="AX20" s="110">
-        <f t="shared" si="68"/>
         <v>0.64295532646048115</v>
       </c>
       <c r="AY20" s="111">
@@ -11209,15 +11128,15 @@
         <v>46095</v>
       </c>
       <c r="BJ20" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60625501202886933</v>
+      </c>
+      <c r="BK20" s="76">
         <f t="shared" si="69"/>
-        <v>0.60625501202886933</v>
-      </c>
-      <c r="BK20" s="76">
+        <v>0.39374498797113072</v>
+      </c>
+      <c r="BL20" s="79">
         <f t="shared" si="70"/>
-        <v>0.39374498797113072</v>
-      </c>
-      <c r="BL20" s="79">
-        <f t="shared" si="71"/>
         <v>23693</v>
       </c>
       <c r="BM20" s="155">
@@ -11238,13 +11157,7 @@
       <c r="BR20" s="157">
         <v>0.37291666666666667</v>
       </c>
-      <c r="BT20" s="14">
-        <v>7088</v>
-      </c>
-      <c r="BV20" s="175">
-        <f t="shared" si="52"/>
-        <v>521</v>
-      </c>
+      <c r="BV20" s="175"/>
     </row>
     <row r="21" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14"/>
@@ -11258,51 +11171,51 @@
         <v>29082</v>
       </c>
       <c r="E21" s="159">
-        <f t="shared" si="53"/>
-        <v>0.75699745547073793</v>
+        <f t="shared" si="52"/>
+        <v>0.75263049308850838</v>
       </c>
       <c r="F21" s="87">
         <f t="shared" si="24"/>
-        <v>22015</v>
+        <v>21888</v>
       </c>
       <c r="G21" s="159">
-        <f t="shared" si="54"/>
-        <v>0.24300254452926209</v>
+        <f t="shared" si="53"/>
+        <v>0.24736950691149165</v>
       </c>
       <c r="H21" s="146">
         <f t="shared" si="26"/>
-        <v>7067</v>
+        <v>7194</v>
       </c>
       <c r="I21" s="160">
+        <f t="shared" si="54"/>
+        <v>6.3484562066792691E-2</v>
+      </c>
+      <c r="J21" s="159">
         <f t="shared" si="55"/>
-        <v>6.3484562066792691E-2</v>
-      </c>
-      <c r="J21" s="159">
+        <v>0.16433522369250159</v>
+      </c>
+      <c r="K21" s="159">
         <f t="shared" si="56"/>
-        <v>0.16433522369250159</v>
-      </c>
-      <c r="K21" s="159">
+        <v>0.17927671678179602</v>
+      </c>
+      <c r="L21" s="161">
         <f t="shared" si="57"/>
-        <v>0.17927671678179602</v>
-      </c>
-      <c r="L21" s="161">
+        <v>0.63317580340264645</v>
+      </c>
+      <c r="M21" s="146">
         <f t="shared" si="58"/>
-        <v>0.63317580340264645</v>
-      </c>
-      <c r="M21" s="146">
+        <v>1775.4092627599243</v>
+      </c>
+      <c r="N21" s="146">
         <f t="shared" si="59"/>
-        <v>1775.4092627599243</v>
-      </c>
-      <c r="N21" s="146">
+        <v>4595.798865784499</v>
+      </c>
+      <c r="O21" s="146">
         <f t="shared" si="60"/>
-        <v>4595.798865784499</v>
-      </c>
-      <c r="O21" s="146">
+        <v>5013.6526615197072</v>
+      </c>
+      <c r="P21" s="146">
         <f t="shared" si="61"/>
-        <v>5013.6526615197072</v>
-      </c>
-      <c r="P21" s="146">
-        <f t="shared" si="62"/>
         <v>17707.394517958412</v>
       </c>
       <c r="Q21" s="56">
@@ -11344,11 +11257,11 @@
         <v>46096</v>
       </c>
       <c r="AC21" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD21" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD21" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE21" s="163">
@@ -11378,11 +11291,11 @@
         <v>46096</v>
       </c>
       <c r="AM21" s="77">
+        <f t="shared" si="64"/>
+        <v>0.29486196319018404</v>
+      </c>
+      <c r="AN21" s="76">
         <f t="shared" si="65"/>
-        <v>0.29486196319018404</v>
-      </c>
-      <c r="AN21" s="76">
-        <f t="shared" si="66"/>
         <v>0.7051380368098159</v>
       </c>
       <c r="AO21" s="150">
@@ -11412,12 +11325,12 @@
         <v>46096</v>
       </c>
       <c r="AW21" s="110">
+        <f t="shared" si="66"/>
+        <v>0.20308250226654578</v>
+      </c>
+      <c r="AX21" s="110">
         <f t="shared" si="67"/>
-        <v>0.23186763372620126</v>
-      </c>
-      <c r="AX21" s="110">
-        <f t="shared" si="68"/>
-        <v>0.76813236627379877</v>
+        <v>0.79691749773345422</v>
       </c>
       <c r="AY21" s="111">
         <f t="shared" si="17"/>
@@ -11428,11 +11341,11 @@
       </c>
       <c r="BA21" s="120">
         <f t="shared" si="18"/>
-        <v>1023</v>
+        <v>896</v>
       </c>
       <c r="BB21" s="113">
-        <f>2818+571</f>
-        <v>3389</v>
+        <f>2818+698</f>
+        <v>3516</v>
       </c>
       <c r="BC21" s="112">
         <v>1625</v>
@@ -11457,15 +11370,15 @@
         <v>46096</v>
       </c>
       <c r="BJ21" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60869781559436731</v>
+      </c>
+      <c r="BK21" s="76">
         <f t="shared" si="69"/>
-        <v>0.60869781559436731</v>
-      </c>
-      <c r="BK21" s="76">
+        <v>0.39130218440563269</v>
+      </c>
+      <c r="BL21" s="79">
         <f t="shared" si="70"/>
-        <v>0.39130218440563269</v>
-      </c>
-      <c r="BL21" s="79">
-        <f t="shared" si="71"/>
         <v>20097</v>
       </c>
       <c r="BM21" s="155">
@@ -11486,13 +11399,7 @@
       <c r="BR21" s="157">
         <v>0.64236111111111116</v>
       </c>
-      <c r="BT21" s="14">
-        <v>7017</v>
-      </c>
-      <c r="BV21" s="175">
-        <f t="shared" si="52"/>
-        <v>-50</v>
-      </c>
+      <c r="BV21" s="175"/>
     </row>
     <row r="22" spans="1:74" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14"/>
@@ -11506,7 +11413,7 @@
         <v>55340</v>
       </c>
       <c r="E22" s="159">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0.86581134803035775</v>
       </c>
       <c r="F22" s="87">
@@ -11514,7 +11421,7 @@
         <v>47914</v>
       </c>
       <c r="G22" s="159">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0.13418865196964222</v>
       </c>
       <c r="H22" s="146">
@@ -11522,35 +11429,35 @@
         <v>7426</v>
       </c>
       <c r="I22" s="160">
+        <f t="shared" si="54"/>
+        <v>0.1202078954657282</v>
+      </c>
+      <c r="J22" s="159">
         <f t="shared" si="55"/>
-        <v>0.1202078954657282</v>
-      </c>
-      <c r="J22" s="159">
+        <v>0.1619499160923473</v>
+      </c>
+      <c r="K22" s="159">
         <f t="shared" si="56"/>
-        <v>0.1619499160923473</v>
-      </c>
-      <c r="K22" s="159">
+        <v>0.17372257260470561</v>
+      </c>
+      <c r="L22" s="161">
         <f t="shared" si="57"/>
-        <v>0.17372257260470561</v>
-      </c>
-      <c r="L22" s="161">
+        <v>0.56794890594196523</v>
+      </c>
+      <c r="M22" s="146">
         <f t="shared" si="58"/>
-        <v>0.56794890594196523</v>
-      </c>
-      <c r="M22" s="146">
+        <v>6488.2211577626795</v>
+      </c>
+      <c r="N22" s="146">
         <f t="shared" si="59"/>
-        <v>6488.2211577626795</v>
-      </c>
-      <c r="N22" s="146">
+        <v>8741.2467210844461</v>
+      </c>
+      <c r="O22" s="146">
         <f t="shared" si="60"/>
-        <v>8741.2467210844461</v>
-      </c>
-      <c r="O22" s="146">
+        <v>9376.6758563389849</v>
+      </c>
+      <c r="P22" s="146">
         <f t="shared" si="61"/>
-        <v>9376.6758563389849</v>
-      </c>
-      <c r="P22" s="146">
-        <f t="shared" si="62"/>
         <v>30655.042198217572</v>
       </c>
       <c r="Q22" s="56">
@@ -11592,11 +11499,11 @@
         <v>46097</v>
       </c>
       <c r="AC22" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD22" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD22" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE22" s="163">
@@ -11626,11 +11533,11 @@
         <v>46097</v>
       </c>
       <c r="AM22" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60784708249496977</v>
+      </c>
+      <c r="AN22" s="76">
         <f t="shared" si="65"/>
-        <v>0.60784708249496977</v>
-      </c>
-      <c r="AN22" s="76">
-        <f t="shared" si="66"/>
         <v>0.39215291750503017</v>
       </c>
       <c r="AO22" s="150">
@@ -11660,11 +11567,11 @@
         <v>46097</v>
       </c>
       <c r="AW22" s="110">
+        <f t="shared" si="66"/>
+        <v>0.61652173913043473</v>
+      </c>
+      <c r="AX22" s="110">
         <f t="shared" si="67"/>
-        <v>0.61652173913043473</v>
-      </c>
-      <c r="AX22" s="110">
-        <f t="shared" si="68"/>
         <v>0.38347826086956521</v>
       </c>
       <c r="AY22" s="111">
@@ -11705,15 +11612,15 @@
         <v>46097</v>
       </c>
       <c r="BJ22" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60638572535069857</v>
+      </c>
+      <c r="BK22" s="76">
         <f t="shared" si="69"/>
-        <v>0.60638572535069857</v>
-      </c>
-      <c r="BK22" s="76">
+        <v>0.39361427464930149</v>
+      </c>
+      <c r="BL22" s="79">
         <f t="shared" si="70"/>
-        <v>0.39361427464930149</v>
-      </c>
-      <c r="BL22" s="79">
-        <f t="shared" si="71"/>
         <v>34859</v>
       </c>
       <c r="BM22" s="155">
@@ -11747,51 +11654,51 @@
         <v>55116</v>
       </c>
       <c r="E23" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86109986210900646</v>
+        <f t="shared" si="52"/>
+        <v>0.85879563103273093</v>
       </c>
       <c r="F23" s="87">
         <f t="shared" si="24"/>
-        <v>47460.38</v>
+        <v>47333.38</v>
       </c>
       <c r="G23" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13890013789099354</v>
+        <f t="shared" si="53"/>
+        <v>0.14120436896726904</v>
       </c>
       <c r="H23" s="146">
         <f t="shared" si="26"/>
-        <v>7655.62</v>
+        <v>7782.62</v>
       </c>
       <c r="I23" s="160">
+        <f t="shared" si="54"/>
+        <v>0.1226827061674125</v>
+      </c>
+      <c r="J23" s="159">
         <f t="shared" si="55"/>
-        <v>0.1226827061674125</v>
-      </c>
-      <c r="J23" s="159">
+        <v>0.16594339302519739</v>
+      </c>
+      <c r="K23" s="159">
         <f t="shared" si="56"/>
-        <v>0.16594339302519739</v>
-      </c>
-      <c r="K23" s="159">
+        <v>0.17258456757967219</v>
+      </c>
+      <c r="L23" s="161">
         <f t="shared" si="57"/>
-        <v>0.17258456757967219</v>
-      </c>
-      <c r="L23" s="161">
+        <v>0.56267563763129946</v>
+      </c>
+      <c r="M23" s="146">
         <f t="shared" si="58"/>
-        <v>0.56267563763129946</v>
-      </c>
-      <c r="M23" s="146">
+        <v>6595.1769181477612</v>
+      </c>
+      <c r="N23" s="146">
         <f t="shared" si="59"/>
-        <v>6595.1769181477612</v>
-      </c>
-      <c r="N23" s="146">
+        <v>8920.784922248562</v>
+      </c>
+      <c r="O23" s="146">
         <f t="shared" si="60"/>
-        <v>8920.784922248562</v>
-      </c>
-      <c r="O23" s="146">
+        <v>9277.8011839480187</v>
+      </c>
+      <c r="P23" s="146">
         <f t="shared" si="61"/>
-        <v>9277.8011839480187</v>
-      </c>
-      <c r="P23" s="146">
-        <f t="shared" si="62"/>
         <v>30248.316927783395</v>
       </c>
       <c r="Q23" s="56">
@@ -11833,11 +11740,11 @@
         <v>46098</v>
       </c>
       <c r="AC23" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD23" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD23" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE23" s="163">
@@ -11867,11 +11774,11 @@
         <v>46098</v>
       </c>
       <c r="AM23" s="77">
+        <f t="shared" si="64"/>
+        <v>0.59567420725081499</v>
+      </c>
+      <c r="AN23" s="76">
         <f t="shared" si="65"/>
-        <v>0.59567420725081499</v>
-      </c>
-      <c r="AN23" s="76">
-        <f t="shared" si="66"/>
         <v>0.40432579274918501</v>
       </c>
       <c r="AO23" s="150">
@@ -11901,12 +11808,12 @@
         <v>46098</v>
       </c>
       <c r="AW23" s="110">
+        <f t="shared" si="66"/>
+        <v>0.5932499173189284</v>
+      </c>
+      <c r="AX23" s="110">
         <f t="shared" si="67"/>
-        <v>0.60725057876750077</v>
-      </c>
-      <c r="AX23" s="110">
-        <f t="shared" si="68"/>
-        <v>0.39274942123249917</v>
+        <v>0.40675008268107155</v>
       </c>
       <c r="AY23" s="111">
         <f t="shared" si="17"/>
@@ -11917,11 +11824,11 @@
       </c>
       <c r="BA23" s="120">
         <f t="shared" si="18"/>
-        <v>5508.37</v>
+        <v>5381.37</v>
       </c>
       <c r="BB23" s="113">
-        <f>2991.63+571</f>
-        <v>3562.63</v>
+        <f>2991.63+698</f>
+        <v>3689.63</v>
       </c>
       <c r="BC23" s="112">
         <v>4182.2</v>
@@ -11946,15 +11853,15 @@
         <v>46098</v>
       </c>
       <c r="BJ23" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60899933721294397</v>
+      </c>
+      <c r="BK23" s="76">
         <f t="shared" si="69"/>
-        <v>0.60899933721294397</v>
-      </c>
-      <c r="BK23" s="76">
+        <v>0.39100066278705597</v>
+      </c>
+      <c r="BL23" s="79">
         <f t="shared" si="70"/>
-        <v>0.39100066278705597</v>
-      </c>
-      <c r="BL23" s="79">
-        <f t="shared" si="71"/>
         <v>34324.75</v>
       </c>
       <c r="BM23" s="155">
@@ -11988,51 +11895,51 @@
         <v>55748</v>
       </c>
       <c r="E24" s="159">
-        <f t="shared" si="53"/>
-        <v>0.86526870919136112</v>
+        <f t="shared" si="52"/>
+        <v>0.86299060055966137</v>
       </c>
       <c r="F24" s="87">
         <f t="shared" si="24"/>
-        <v>48237</v>
+        <v>48110</v>
       </c>
       <c r="G24" s="159">
-        <f t="shared" si="54"/>
-        <v>0.13473129080863888</v>
+        <f t="shared" si="53"/>
+        <v>0.13700939944033866</v>
       </c>
       <c r="H24" s="146">
         <f t="shared" si="26"/>
-        <v>7511</v>
+        <v>7638</v>
       </c>
       <c r="I24" s="160">
+        <f t="shared" si="54"/>
+        <v>0.12229982134156245</v>
+      </c>
+      <c r="J24" s="159">
         <f t="shared" si="55"/>
-        <v>0.12229982134156245</v>
-      </c>
-      <c r="J24" s="159">
+        <v>0.16421958746142601</v>
+      </c>
+      <c r="K24" s="159">
         <f t="shared" si="56"/>
-        <v>0.16421958746142601</v>
-      </c>
-      <c r="K24" s="159">
+        <v>0.17212093760616012</v>
+      </c>
+      <c r="L24" s="161">
         <f t="shared" si="57"/>
-        <v>0.17212093760616012</v>
-      </c>
-      <c r="L24" s="161">
+        <v>0.56535650479129451</v>
+      </c>
+      <c r="M24" s="146">
         <f t="shared" si="58"/>
-        <v>0.56535650479129451</v>
-      </c>
-      <c r="M24" s="146">
+        <v>6676.7141464999186</v>
+      </c>
+      <c r="N24" s="146">
         <f t="shared" si="59"/>
-        <v>6676.7141464999186</v>
-      </c>
-      <c r="N24" s="146">
+        <v>8965.2399382816293</v>
+      </c>
+      <c r="O24" s="146">
         <f t="shared" si="60"/>
-        <v>8965.2399382816293</v>
-      </c>
-      <c r="O24" s="146">
+        <v>9396.5983467330989</v>
+      </c>
+      <c r="P24" s="146">
         <f t="shared" si="61"/>
-        <v>9396.5983467330989</v>
-      </c>
-      <c r="P24" s="146">
-        <f t="shared" si="62"/>
         <v>30864.507666071142</v>
       </c>
       <c r="Q24" s="56">
@@ -12074,11 +11981,11 @@
         <v>46099</v>
       </c>
       <c r="AC24" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD24" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD24" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE24" s="163">
@@ -12108,11 +12015,11 @@
         <v>46099</v>
       </c>
       <c r="AM24" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60419345267530411</v>
+      </c>
+      <c r="AN24" s="76">
         <f t="shared" si="65"/>
-        <v>0.60419345267530411</v>
-      </c>
-      <c r="AN24" s="76">
-        <f t="shared" si="66"/>
         <v>0.39580654732469589</v>
       </c>
       <c r="AO24" s="150">
@@ -12142,12 +12049,12 @@
         <v>46099</v>
       </c>
       <c r="AW24" s="110">
+        <f t="shared" si="66"/>
+        <v>0.60131578947368425</v>
+      </c>
+      <c r="AX24" s="110">
         <f t="shared" si="67"/>
-        <v>0.61524122807017545</v>
-      </c>
-      <c r="AX24" s="110">
-        <f t="shared" si="68"/>
-        <v>0.38475877192982455</v>
+        <v>0.39868421052631581</v>
       </c>
       <c r="AY24" s="111">
         <f t="shared" si="17"/>
@@ -12158,11 +12065,11 @@
       </c>
       <c r="BA24" s="120">
         <f t="shared" si="18"/>
-        <v>5611</v>
+        <v>5484</v>
       </c>
       <c r="BB24" s="113">
-        <f>2938+571</f>
-        <v>3509</v>
+        <f>2938+698</f>
+        <v>3636</v>
       </c>
       <c r="BC24" s="112">
         <v>4036</v>
@@ -12187,15 +12094,15 @@
         <v>46099</v>
       </c>
       <c r="BJ24" s="78">
+        <f t="shared" si="68"/>
+        <v>0.60636616966876378</v>
+      </c>
+      <c r="BK24" s="76">
         <f t="shared" si="69"/>
-        <v>0.60636616966876378</v>
-      </c>
-      <c r="BK24" s="76">
+        <v>0.39363383033123617</v>
+      </c>
+      <c r="BL24" s="79">
         <f t="shared" si="70"/>
-        <v>0.39363383033123617</v>
-      </c>
-      <c r="BL24" s="79">
-        <f t="shared" si="71"/>
         <v>34809</v>
       </c>
       <c r="BM24" s="155">
@@ -12229,51 +12136,51 @@
         <v>55416</v>
       </c>
       <c r="E25" s="159">
-        <f t="shared" ref="E25:E36" si="81">F25/D25</f>
-        <v>0.86429911938790238</v>
+        <f t="shared" ref="E25:E36" si="80">F25/D25</f>
+        <v>0.86200736249458643</v>
       </c>
       <c r="F25" s="87">
         <f t="shared" si="24"/>
-        <v>47896</v>
+        <v>47769</v>
       </c>
       <c r="G25" s="159">
-        <f t="shared" ref="G25:G36" si="82">H25/D25</f>
-        <v>0.13570088061209759</v>
+        <f t="shared" ref="G25:G36" si="81">H25/D25</f>
+        <v>0.1379926375054136</v>
       </c>
       <c r="H25" s="146">
         <f t="shared" si="26"/>
-        <v>7520</v>
+        <v>7647</v>
       </c>
       <c r="I25" s="160">
-        <f t="shared" ref="I25:I36" si="83">AE25/(AE25+AO25+BL25+AY25)</f>
+        <f t="shared" ref="I25:I36" si="82">AE25/(AE25+AO25+BL25+AY25)</f>
         <v>0.12118496309211491</v>
       </c>
       <c r="J25" s="159">
-        <f t="shared" ref="J25:J36" si="84">AO25/(AE25+AO25+BL25+AY25)</f>
+        <f t="shared" ref="J25:J36" si="83">AO25/(AE25+AO25+BL25+AY25)</f>
         <v>0.16091186103733154</v>
       </c>
       <c r="K25" s="159">
-        <f t="shared" ref="K25:K36" si="85">AY25/(AF25+AP25+BM25+AZ25+AY25)</f>
+        <f t="shared" ref="K25:K36" si="84">AY25/(AF25+AP25+BM25+AZ25+AY25)</f>
         <v>0.17304347826086958</v>
       </c>
       <c r="L25" s="161">
-        <f t="shared" ref="L25:L36" si="86">BL25/(AE25+AO25+BL25+AY25)</f>
+        <f t="shared" ref="L25:L36" si="85">BL25/(AE25+AO25+BL25+AY25)</f>
         <v>0.56873991754794762</v>
       </c>
       <c r="M25" s="146">
-        <f t="shared" ref="M25:M35" si="87">(S25+T25)*I25</f>
+        <f t="shared" ref="M25:M35" si="86">(S25+T25)*I25</f>
         <v>6560.3479769916403</v>
       </c>
       <c r="N25" s="146">
-        <f t="shared" ref="N25:N35" si="88">(S25+T25)*J25</f>
+        <f t="shared" ref="N25:N35" si="87">(S25+T25)*J25</f>
         <v>8710.9635972559427</v>
       </c>
       <c r="O25" s="146">
-        <f t="shared" ref="O25:O35" si="89">(S25+T25)*K25</f>
+        <f t="shared" ref="O25:O35" si="88">(S25+T25)*K25</f>
         <v>9367.7086956521744</v>
       </c>
       <c r="P25" s="146">
-        <f t="shared" ref="P25:P35" si="90">(S25+T25)*L25</f>
+        <f t="shared" ref="P25:P35" si="89">(S25+T25)*L25</f>
         <v>30788.735436458144</v>
       </c>
       <c r="Q25" s="56">
@@ -12315,11 +12222,11 @@
         <v>46100</v>
       </c>
       <c r="AC25" s="76">
+        <f t="shared" si="62"/>
+        <v>1</v>
+      </c>
+      <c r="AD25" s="162">
         <f t="shared" si="63"/>
-        <v>1</v>
-      </c>
-      <c r="AD25" s="162">
-        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="AE25" s="163">
@@ -12349,11 +12256,11 @@
         <v>46100</v>
       </c>
       <c r="AM25" s="77">
+        <f t="shared" si="64"/>
+        <v>0.60303797468354425</v>
+      </c>
+      <c r="AN25" s="76">
         <f t="shared" si="65"/>
-        <v>0.60303797468354425</v>
-      </c>
-      <c r="AN25" s="76">
-        <f t="shared" si="66"/>
         <v>0.39696202531645569</v>
       </c>
       <c r="AO25" s="150">
@@ -12383,12 +12290,12 @@
         <v>46100</v>
       </c>
       <c r="AW25" s="169">
+        <f t="shared" si="66"/>
+        <v>0.59285558225912172</v>
+      </c>
+      <c r="AX25" s="169">
         <f t="shared" si="67"/>
-        <v>0.60672929866724934</v>
-      </c>
-      <c r="AX25" s="169">
-        <f t="shared" si="68"/>
-        <v>0.39327070133275072</v>
+        <v>0.40714441774087828</v>
       </c>
       <c r="AY25" s="111">
         <f t="shared" si="17"/>
@@ -12399,11 +12306,11 @@
       </c>
       <c r="BA25" s="120">
         <f t="shared" si="18"/>
-        <v>5554</v>
+        <v>5427</v>
       </c>
       <c r="BB25" s="113">
-        <f>3029+571</f>
-        <v>3600</v>
+        <f>3029+698</f>
+        <v>3727</v>
       </c>
       <c r="BC25" s="112">
         <v>3973</v>
@@ -12428,15 +12335,15 @@
         <v>46100</v>
       </c>
       <c r="BJ25" s="170">
+        <f t="shared" si="68"/>
+        <v>0.60739764490158443</v>
+      </c>
+      <c r="BK25" s="76">
         <f t="shared" si="69"/>
-        <v>0.60739764490158443</v>
-      </c>
-      <c r="BK25" s="76">
+        <v>0.39260235509841562</v>
+      </c>
+      <c r="BL25" s="79">
         <f t="shared" si="70"/>
-        <v>0.39260235509841562</v>
-      </c>
-      <c r="BL25" s="79">
-        <f t="shared" si="71"/>
         <v>34903</v>
       </c>
       <c r="BM25" s="155">
@@ -12470,51 +12377,51 @@
         <v>55405</v>
       </c>
       <c r="E26" s="159">
-        <f t="shared" si="81"/>
-        <v>0.86582438408085916</v>
+        <f t="shared" si="80"/>
+        <v>0.8635321721866257</v>
       </c>
       <c r="F26" s="87">
         <f t="shared" si="24"/>
-        <v>47971</v>
+        <v>47844</v>
       </c>
       <c r="G26" s="159">
-        <f t="shared" si="82"/>
-        <v>0.13417561591914087</v>
+        <f t="shared" si="81"/>
+        <v>0.13646782781337424</v>
       </c>
       <c r="H26" s="146">
         <f t="shared" si="26"/>
-        <v>7434</v>
+        <v>7561</v>
       </c>
       <c r="I26" s="160">
+        <f t="shared" si="82"/>
+        <v>0.12153883851997059</v>
+      </c>
+      <c r="J26" s="159">
         <f t="shared" si="83"/>
-        <v>0.12153883851997059</v>
-      </c>
-      <c r="J26" s="159">
+        <v>0.1604181981540472</v>
+      </c>
+      <c r="K26" s="159">
         <f t="shared" si="84"/>
-        <v>0.1604181981540472</v>
-      </c>
-      <c r="K26" s="159">
+        <v>0.17190019922208519</v>
+      </c>
+      <c r="L26" s="161">
         <f t="shared" si="85"/>
-        <v>0.17190019922208519</v>
-      </c>
-      <c r="L26" s="161">
+        <v>0.5700400228702116</v>
+      </c>
+      <c r="M26" s="146">
         <f t="shared" si="86"/>
-        <v>0.5700400228702116</v>
-      </c>
-      <c r="M26" s="146">
+        <v>6581.3281058564071</v>
+      </c>
+      <c r="N26" s="146">
         <f t="shared" si="87"/>
-        <v>6581.3281058564071</v>
-      </c>
-      <c r="N26" s="146">
+        <v>8686.6454300416553</v>
+      </c>
+      <c r="O26" s="146">
         <f t="shared" si="88"/>
-        <v>8686.6454300416553</v>
-      </c>
-      <c r="O26" s="146">
+        <v>9308.395787875912</v>
+      </c>
+      <c r="P26" s="146">
         <f t="shared" si="89"/>
-        <v>9308.395787875912</v>
-      </c>
-      <c r="P26" s="146">
-        <f t="shared" si="90"/>
         <v>30867.66723842196</v>
       </c>
       <c r="Q26" s="56">
@@ -12556,11 +12463,11 @@
         <v>46101</v>
       </c>
       <c r="AC26" s="76">
-        <f t="shared" ref="AC26:AC36" si="91">+AF26/AE26</f>
+        <f t="shared" ref="AC26:AC36" si="90">+AF26/AE26</f>
         <v>1</v>
       </c>
       <c r="AD26" s="162">
-        <f t="shared" ref="AD26:AD36" si="92">+AG26/AE26</f>
+        <f t="shared" ref="AD26:AD36" si="91">+AG26/AE26</f>
         <v>0</v>
       </c>
       <c r="AE26" s="163">
@@ -12590,11 +12497,11 @@
         <v>46101</v>
       </c>
       <c r="AM26" s="77">
-        <f t="shared" ref="AM26:AM36" si="93">+AP26/AO26</f>
+        <f t="shared" ref="AM26:AM36" si="92">+AP26/AO26</f>
         <v>0.60641547861507128</v>
       </c>
       <c r="AN26" s="76">
-        <f t="shared" ref="AN26:AN36" si="94">+AQ26/AO26</f>
+        <f t="shared" ref="AN26:AN36" si="93">+AQ26/AO26</f>
         <v>0.39358452138492872</v>
       </c>
       <c r="AO26" s="150">
@@ -12624,12 +12531,12 @@
         <v>46101</v>
       </c>
       <c r="AW26" s="110">
-        <f t="shared" ref="AW26:AW36" si="95">BA26/AZ26</f>
-        <v>0.60607064017660039</v>
+        <f t="shared" ref="AW26:AW36" si="94">BA26/AZ26</f>
+        <v>0.59205298013245033</v>
       </c>
       <c r="AX26" s="110">
-        <f t="shared" ref="AX26:AX36" si="96">BB26/AZ26</f>
-        <v>0.39392935982339955</v>
+        <f t="shared" ref="AX26:AX36" si="95">BB26/AZ26</f>
+        <v>0.40794701986754967</v>
       </c>
       <c r="AY26" s="111">
         <f t="shared" si="17"/>
@@ -12640,11 +12547,11 @@
       </c>
       <c r="BA26" s="120">
         <f t="shared" si="18"/>
-        <v>5491</v>
+        <v>5364</v>
       </c>
       <c r="BB26" s="113">
-        <f>2998+571</f>
-        <v>3569</v>
+        <f>2998+698</f>
+        <v>3696</v>
       </c>
       <c r="BC26" s="112">
         <v>3995</v>
@@ -12669,15 +12576,15 @@
         <v>46101</v>
       </c>
       <c r="BJ26" s="78">
-        <f t="shared" ref="BJ26:BJ36" si="97">+BM26/BL26</f>
+        <f t="shared" ref="BJ26:BJ36" si="96">+BM26/BL26</f>
         <v>0.60725032239575871</v>
       </c>
       <c r="BK26" s="76">
-        <f t="shared" ref="BK26:BK36" si="98">+BN26/BL26</f>
+        <f t="shared" ref="BK26:BK36" si="97">+BN26/BL26</f>
         <v>0.39274967760424129</v>
       </c>
       <c r="BL26" s="79">
-        <f t="shared" ref="BL26:BL36" si="99">BM26+BN26</f>
+        <f t="shared" ref="BL26:BL36" si="98">BM26+BN26</f>
         <v>34895</v>
       </c>
       <c r="BM26" s="155">
@@ -12711,51 +12618,51 @@
         <v>34250</v>
       </c>
       <c r="E27" s="159">
-        <f t="shared" si="81"/>
-        <v>0.81643795620437953</v>
+        <f t="shared" si="80"/>
+        <v>0.81272992700729929</v>
       </c>
       <c r="F27" s="87">
         <f t="shared" si="24"/>
-        <v>27963</v>
+        <v>27836</v>
       </c>
       <c r="G27" s="159">
-        <f t="shared" si="82"/>
-        <v>0.18356204379562044</v>
+        <f t="shared" si="81"/>
+        <v>0.18727007299270074</v>
       </c>
       <c r="H27" s="146">
         <f t="shared" si="26"/>
-        <v>6287</v>
+        <v>6414</v>
       </c>
       <c r="I27" s="160">
+        <f t="shared" si="82"/>
+        <v>7.4734936643392813E-2</v>
+      </c>
+      <c r="J27" s="159">
         <f t="shared" si="83"/>
-        <v>7.4734936643392813E-2</v>
-      </c>
-      <c r="J27" s="159">
+        <v>0.12878200155159039</v>
+      </c>
+      <c r="K27" s="159">
         <f t="shared" si="84"/>
-        <v>0.12878200155159039</v>
-      </c>
-      <c r="K27" s="159">
+        <v>0.17231512685191072</v>
+      </c>
+      <c r="L27" s="161">
         <f t="shared" si="85"/>
-        <v>0.17231512685191072</v>
-      </c>
-      <c r="L27" s="161">
+        <v>0.656322730799069</v>
+      </c>
+      <c r="M27" s="146">
         <f t="shared" si="86"/>
-        <v>0.656322730799069</v>
-      </c>
-      <c r="M27" s="146">
+        <v>2487.9260408585469</v>
+      </c>
+      <c r="N27" s="146">
         <f t="shared" si="87"/>
-        <v>2487.9260408585469</v>
-      </c>
-      <c r="N27" s="146">
+        <v>4287.1528316524445</v>
+      </c>
+      <c r="O27" s="146">
         <f t="shared" si="88"/>
-        <v>4287.1528316524445</v>
-      </c>
-      <c r="O27" s="146">
+        <v>5736.3705729001076</v>
+      </c>
+      <c r="P27" s="146">
         <f t="shared" si="89"/>
-        <v>5736.3705729001076</v>
-      </c>
-      <c r="P27" s="146">
-        <f t="shared" si="90"/>
         <v>21848.983708301006</v>
       </c>
       <c r="Q27" s="56">
@@ -12797,11 +12704,11 @@
         <v>46102</v>
       </c>
       <c r="AC27" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD27" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD27" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE27" s="163">
@@ -12831,11 +12738,11 @@
         <v>46102</v>
       </c>
       <c r="AM27" s="77">
+        <f t="shared" si="92"/>
+        <v>0.42851405622489958</v>
+      </c>
+      <c r="AN27" s="76">
         <f t="shared" si="93"/>
-        <v>0.42851405622489958</v>
-      </c>
-      <c r="AN27" s="76">
-        <f t="shared" si="94"/>
         <v>0.57148594377510042</v>
       </c>
       <c r="AO27" s="150">
@@ -12865,12 +12772,12 @@
         <v>46102</v>
       </c>
       <c r="AW27" s="110">
+        <f t="shared" si="94"/>
+        <v>0.34169741697416972</v>
+      </c>
+      <c r="AX27" s="110">
         <f t="shared" si="95"/>
-        <v>0.36512915129151291</v>
-      </c>
-      <c r="AX27" s="110">
-        <f t="shared" si="96"/>
-        <v>0.63487084870848709</v>
+        <v>0.65830258302583022</v>
       </c>
       <c r="AY27" s="111">
         <f t="shared" si="17"/>
@@ -12881,11 +12788,11 @@
       </c>
       <c r="BA27" s="120">
         <f t="shared" si="18"/>
-        <v>1979</v>
+        <v>1852</v>
       </c>
       <c r="BB27" s="113">
-        <f>2870+571</f>
-        <v>3441</v>
+        <f>2870+698</f>
+        <v>3568</v>
       </c>
       <c r="BC27" s="112">
         <v>1590</v>
@@ -12910,15 +12817,15 @@
         <v>46102</v>
       </c>
       <c r="BJ27" s="78">
+        <f t="shared" si="96"/>
+        <v>0.6142631993695824</v>
+      </c>
+      <c r="BK27" s="76">
         <f t="shared" si="97"/>
-        <v>0.6142631993695824</v>
-      </c>
-      <c r="BK27" s="76">
+        <v>0.38573680063041765</v>
+      </c>
+      <c r="BL27" s="79">
         <f t="shared" si="98"/>
-        <v>0.38573680063041765</v>
-      </c>
-      <c r="BL27" s="79">
-        <f t="shared" si="99"/>
         <v>25380</v>
       </c>
       <c r="BM27" s="155">
@@ -12952,51 +12859,51 @@
         <v>28302</v>
       </c>
       <c r="E28" s="159">
-        <f t="shared" si="81"/>
-        <v>0.75899229736414386</v>
+        <f t="shared" si="80"/>
+        <v>0.7545049819800721</v>
       </c>
       <c r="F28" s="87">
         <f t="shared" si="24"/>
-        <v>21481</v>
+        <v>21354</v>
       </c>
       <c r="G28" s="159">
-        <f t="shared" si="82"/>
-        <v>0.24100770263585614</v>
+        <f t="shared" si="81"/>
+        <v>0.24549501801992793</v>
       </c>
       <c r="H28" s="146">
         <f t="shared" si="26"/>
-        <v>6821</v>
+        <v>6948</v>
       </c>
       <c r="I28" s="160">
+        <f t="shared" si="82"/>
+        <v>6.1168318114111782E-2</v>
+      </c>
+      <c r="J28" s="159">
         <f t="shared" si="83"/>
-        <v>6.1168318114111782E-2</v>
-      </c>
-      <c r="J28" s="159">
+        <v>0.1660514215400557</v>
+      </c>
+      <c r="K28" s="159">
         <f t="shared" si="84"/>
-        <v>0.1660514215400557</v>
-      </c>
-      <c r="K28" s="159">
+        <v>0.17945705534343137</v>
+      </c>
+      <c r="L28" s="161">
         <f t="shared" si="85"/>
-        <v>0.17945705534343137</v>
-      </c>
-      <c r="L28" s="161">
+        <v>0.63428534421345772</v>
+      </c>
+      <c r="M28" s="146">
         <f t="shared" si="86"/>
-        <v>0.63428534421345772</v>
-      </c>
-      <c r="M28" s="146">
+        <v>1615.332944757464</v>
+      </c>
+      <c r="N28" s="146">
         <f t="shared" si="87"/>
-        <v>1615.332944757464</v>
-      </c>
-      <c r="N28" s="146">
+        <v>4385.0859400297913</v>
+      </c>
+      <c r="O28" s="146">
         <f t="shared" si="88"/>
-        <v>4385.0859400297913</v>
-      </c>
-      <c r="O28" s="146">
+        <v>4739.1019175093361</v>
+      </c>
+      <c r="P28" s="146">
         <f t="shared" si="89"/>
-        <v>4739.1019175093361</v>
-      </c>
-      <c r="P28" s="146">
-        <f t="shared" si="90"/>
         <v>16750.207369988992</v>
       </c>
       <c r="Q28" s="56">
@@ -13038,11 +12945,11 @@
         <v>46103</v>
       </c>
       <c r="AC28" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD28" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD28" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE28" s="163">
@@ -13072,11 +12979,11 @@
         <v>46103</v>
       </c>
       <c r="AM28" s="77">
+        <f t="shared" si="92"/>
+        <v>0.29153666146645868</v>
+      </c>
+      <c r="AN28" s="76">
         <f t="shared" si="93"/>
-        <v>0.29153666146645868</v>
-      </c>
-      <c r="AN28" s="76">
-        <f t="shared" si="94"/>
         <v>0.70846333853354138</v>
       </c>
       <c r="AO28" s="150">
@@ -13106,12 +13013,12 @@
         <v>46103</v>
       </c>
       <c r="AW28" s="110">
+        <f t="shared" si="94"/>
+        <v>0.22492401215805471</v>
+      </c>
+      <c r="AX28" s="110">
         <f t="shared" si="95"/>
-        <v>0.25461772270282906</v>
-      </c>
-      <c r="AX28" s="110">
-        <f t="shared" si="96"/>
-        <v>0.74538227729717088</v>
+        <v>0.77507598784194531</v>
       </c>
       <c r="AY28" s="111">
         <f t="shared" si="17"/>
@@ -13122,11 +13029,11 @@
       </c>
       <c r="BA28" s="120">
         <f t="shared" si="18"/>
-        <v>1089</v>
+        <v>962</v>
       </c>
       <c r="BB28" s="113">
-        <f>2617+571</f>
-        <v>3188</v>
+        <f>2617+698</f>
+        <v>3315</v>
       </c>
       <c r="BC28" s="112">
         <v>1442</v>
@@ -13151,15 +13058,15 @@
         <v>46103</v>
       </c>
       <c r="BJ28" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60725954666122117</v>
+      </c>
+      <c r="BK28" s="76">
         <f t="shared" si="97"/>
-        <v>0.60725954666122117</v>
-      </c>
-      <c r="BK28" s="76">
+        <v>0.39274045333877883</v>
+      </c>
+      <c r="BL28" s="79">
         <f t="shared" si="98"/>
-        <v>0.39274045333877883</v>
-      </c>
-      <c r="BL28" s="79">
-        <f t="shared" si="99"/>
         <v>19588</v>
       </c>
       <c r="BM28" s="155">
@@ -13193,51 +13100,51 @@
         <v>55496</v>
       </c>
       <c r="E29" s="159">
-        <f t="shared" si="81"/>
-        <v>0.87159434914228051</v>
+        <f t="shared" si="80"/>
+        <v>0.86930589592042673</v>
       </c>
       <c r="F29" s="87">
         <f t="shared" si="24"/>
-        <v>48370</v>
+        <v>48243</v>
       </c>
       <c r="G29" s="159">
-        <f t="shared" si="82"/>
-        <v>0.12840565085771949</v>
+        <f t="shared" si="81"/>
+        <v>0.1306941040795733</v>
       </c>
       <c r="H29" s="146">
         <f t="shared" si="26"/>
-        <v>7126</v>
+        <v>7253</v>
       </c>
       <c r="I29" s="160">
+        <f t="shared" si="82"/>
+        <v>0.12204667575587456</v>
+      </c>
+      <c r="J29" s="159">
         <f t="shared" si="83"/>
-        <v>0.12204667575587456</v>
-      </c>
-      <c r="J29" s="159">
+        <v>0.15962787713529553</v>
+      </c>
+      <c r="K29" s="159">
         <f t="shared" si="84"/>
-        <v>0.15962787713529553</v>
-      </c>
-      <c r="K29" s="159">
+        <v>0.17117486084479774</v>
+      </c>
+      <c r="L29" s="161">
         <f t="shared" si="85"/>
-        <v>0.17117486084479774</v>
-      </c>
-      <c r="L29" s="161">
+        <v>0.5708396824123827</v>
+      </c>
+      <c r="M29" s="146">
         <f t="shared" si="86"/>
-        <v>0.5708396824123827</v>
-      </c>
-      <c r="M29" s="146">
+        <v>6643.4887480952757</v>
+      </c>
+      <c r="N29" s="146">
         <f t="shared" si="87"/>
-        <v>6643.4887480952757</v>
-      </c>
-      <c r="N29" s="146">
+        <v>8689.1838639826765</v>
+      </c>
+      <c r="O29" s="146">
         <f t="shared" si="88"/>
-        <v>8689.1838639826765</v>
-      </c>
-      <c r="O29" s="146">
+        <v>9317.7323752257198</v>
+      </c>
+      <c r="P29" s="146">
         <f t="shared" si="89"/>
-        <v>9317.7323752257198</v>
-      </c>
-      <c r="P29" s="146">
-        <f t="shared" si="90"/>
         <v>31073.087272435641</v>
       </c>
       <c r="Q29" s="56">
@@ -13279,11 +13186,11 @@
         <v>46104</v>
       </c>
       <c r="AC29" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD29" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD29" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE29" s="163">
@@ -13313,11 +13220,11 @@
         <v>46104</v>
       </c>
       <c r="AM29" s="77">
+        <f t="shared" si="92"/>
+        <v>0.62027733118971062</v>
+      </c>
+      <c r="AN29" s="76">
         <f t="shared" si="93"/>
-        <v>0.62027733118971062</v>
-      </c>
-      <c r="AN29" s="76">
-        <f t="shared" si="94"/>
         <v>0.37972266881028938</v>
       </c>
       <c r="AO29" s="150">
@@ -13347,12 +13254,12 @@
         <v>46104</v>
       </c>
       <c r="AW29" s="110">
+        <f t="shared" si="94"/>
+        <v>0.62218597063621528</v>
+      </c>
+      <c r="AX29" s="110">
         <f t="shared" si="95"/>
-        <v>0.63599782490483958</v>
-      </c>
-      <c r="AX29" s="110">
-        <f t="shared" si="96"/>
-        <v>0.36400217509516042</v>
+        <v>0.37781402936378466</v>
       </c>
       <c r="AY29" s="111">
         <f t="shared" si="17"/>
@@ -13363,11 +13270,11 @@
       </c>
       <c r="BA29" s="120">
         <f t="shared" si="18"/>
-        <v>5848</v>
+        <v>5721</v>
       </c>
       <c r="BB29" s="113">
-        <f>2776+571</f>
-        <v>3347</v>
+        <f>2776+698</f>
+        <v>3474</v>
       </c>
       <c r="BC29" s="112">
         <v>3842</v>
@@ -13392,15 +13299,15 @@
         <v>46104</v>
       </c>
       <c r="BJ29" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60538368597038406</v>
+      </c>
+      <c r="BK29" s="76">
         <f t="shared" si="97"/>
-        <v>0.60538368597038406</v>
-      </c>
-      <c r="BK29" s="76">
+        <v>0.39461631402961589</v>
+      </c>
+      <c r="BL29" s="79">
         <f t="shared" si="98"/>
-        <v>0.39461631402961589</v>
-      </c>
-      <c r="BL29" s="79">
-        <f t="shared" si="99"/>
         <v>35589</v>
       </c>
       <c r="BM29" s="155">
@@ -13434,51 +13341,51 @@
         <v>55282</v>
       </c>
       <c r="E30" s="159">
-        <f t="shared" si="81"/>
-        <v>0.86729857819905209</v>
+        <f t="shared" si="80"/>
+        <v>0.86500126623494089</v>
       </c>
       <c r="F30" s="87">
         <f t="shared" si="24"/>
-        <v>47946</v>
+        <v>47819</v>
       </c>
       <c r="G30" s="159">
-        <f t="shared" si="82"/>
-        <v>0.13270142180094788</v>
+        <f t="shared" si="81"/>
+        <v>0.13499873376505916</v>
       </c>
       <c r="H30" s="146">
         <f t="shared" si="26"/>
-        <v>7336</v>
+        <v>7463</v>
       </c>
       <c r="I30" s="160">
+        <f t="shared" si="82"/>
+        <v>0.1215191932335719</v>
+      </c>
+      <c r="J30" s="159">
         <f t="shared" si="83"/>
-        <v>0.1215191932335719</v>
-      </c>
-      <c r="J30" s="159">
+        <v>0.16106050748210801</v>
+      </c>
+      <c r="K30" s="159">
         <f t="shared" si="84"/>
-        <v>0.16106050748210801</v>
-      </c>
-      <c r="K30" s="159">
+        <v>0.17093532789362345</v>
+      </c>
+      <c r="L30" s="161">
         <f t="shared" si="85"/>
-        <v>0.17093532789362345</v>
-      </c>
-      <c r="L30" s="161">
+        <v>0.57021795705920619</v>
+      </c>
+      <c r="M30" s="146">
         <f t="shared" si="86"/>
-        <v>0.57021795705920619</v>
-      </c>
-      <c r="M30" s="146">
+        <v>6529.8338484059859</v>
+      </c>
+      <c r="N30" s="146">
         <f t="shared" si="87"/>
-        <v>6529.8338484059859</v>
-      </c>
-      <c r="N30" s="146">
+        <v>8654.5863695510743</v>
+      </c>
+      <c r="O30" s="146">
         <f t="shared" si="88"/>
-        <v>8654.5863695510743</v>
-      </c>
-      <c r="O30" s="146">
+        <v>9185.209844363857</v>
+      </c>
+      <c r="P30" s="146">
         <f t="shared" si="89"/>
-        <v>9185.209844363857</v>
-      </c>
-      <c r="P30" s="146">
-        <f t="shared" si="90"/>
         <v>30640.661922576444</v>
       </c>
       <c r="Q30" s="56">
@@ -13520,11 +13427,11 @@
         <v>46105</v>
       </c>
       <c r="AC30" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD30" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD30" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE30" s="163">
@@ -13554,11 +13461,11 @@
         <v>46105</v>
       </c>
       <c r="AM30" s="77">
+        <f t="shared" si="92"/>
+        <v>0.61371440113108466</v>
+      </c>
+      <c r="AN30" s="76">
         <f t="shared" si="93"/>
-        <v>0.61371440113108466</v>
-      </c>
-      <c r="AN30" s="76">
-        <f t="shared" si="94"/>
         <v>0.38628559886891539</v>
       </c>
       <c r="AO30" s="150">
@@ -13588,12 +13495,12 @@
         <v>46105</v>
       </c>
       <c r="AW30" s="110">
+        <f t="shared" si="94"/>
+        <v>0.59801104972375696</v>
+      </c>
+      <c r="AX30" s="110">
         <f t="shared" si="95"/>
-        <v>0.61204419889502759</v>
-      </c>
-      <c r="AX30" s="110">
-        <f t="shared" si="96"/>
-        <v>0.38795580110497235</v>
+        <v>0.4019889502762431</v>
       </c>
       <c r="AY30" s="111">
         <f t="shared" si="17"/>
@@ -13604,11 +13511,11 @@
       </c>
       <c r="BA30" s="120">
         <f t="shared" si="18"/>
-        <v>5539</v>
+        <v>5412</v>
       </c>
       <c r="BB30" s="113">
-        <f>2940+571</f>
-        <v>3511</v>
+        <f>2940+698</f>
+        <v>3638</v>
       </c>
       <c r="BC30" s="112">
         <v>4243</v>
@@ -13633,15 +13540,15 @@
         <v>46105</v>
       </c>
       <c r="BJ30" s="78">
+        <f t="shared" si="96"/>
+        <v>0.6074678380922498</v>
+      </c>
+      <c r="BK30" s="76">
         <f t="shared" si="97"/>
-        <v>0.6074678380922498</v>
-      </c>
-      <c r="BK30" s="76">
+        <v>0.39253216190775025</v>
+      </c>
+      <c r="BL30" s="79">
         <f t="shared" si="98"/>
-        <v>0.39253216190775025</v>
-      </c>
-      <c r="BL30" s="79">
-        <f t="shared" si="99"/>
         <v>35057</v>
       </c>
       <c r="BM30" s="155">
@@ -13675,51 +13582,51 @@
         <v>57344</v>
       </c>
       <c r="E31" s="159">
-        <f t="shared" si="81"/>
-        <v>0.8709368024553571</v>
+        <f t="shared" si="80"/>
+        <v>0.8687220982142857</v>
       </c>
       <c r="F31" s="87">
         <f t="shared" si="24"/>
-        <v>49943</v>
+        <v>49816</v>
       </c>
       <c r="G31" s="159">
-        <f t="shared" si="82"/>
-        <v>0.12906319754464285</v>
+        <f t="shared" si="81"/>
+        <v>0.13127790178571427</v>
       </c>
       <c r="H31" s="146">
         <f t="shared" si="26"/>
-        <v>7401</v>
+        <v>7528</v>
       </c>
       <c r="I31" s="160">
+        <f t="shared" si="82"/>
+        <v>0.1175089427819537</v>
+      </c>
+      <c r="J31" s="159">
         <f t="shared" si="83"/>
-        <v>0.1175089427819537</v>
-      </c>
-      <c r="J31" s="159">
+        <v>0.15660505208087111</v>
+      </c>
+      <c r="K31" s="159">
         <f t="shared" si="84"/>
-        <v>0.15660505208087111</v>
-      </c>
-      <c r="K31" s="159">
+        <v>0.16935914675705049</v>
+      </c>
+      <c r="L31" s="161">
         <f t="shared" si="85"/>
-        <v>0.16935914675705049</v>
-      </c>
-      <c r="L31" s="161">
+        <v>0.58100505838415351</v>
+      </c>
+      <c r="M31" s="146">
         <f t="shared" si="86"/>
-        <v>0.58100505838415351</v>
-      </c>
-      <c r="M31" s="146">
+        <v>6580.5007957894077</v>
+      </c>
+      <c r="N31" s="146">
         <f t="shared" si="87"/>
-        <v>6580.5007957894077</v>
-      </c>
-      <c r="N31" s="146">
+        <v>8769.8829165287825</v>
+      </c>
+      <c r="O31" s="146">
         <f t="shared" si="88"/>
-        <v>8769.8829165287825</v>
-      </c>
-      <c r="O31" s="146">
+        <v>9484.1122183948282</v>
+      </c>
+      <c r="P31" s="146">
         <f t="shared" si="89"/>
-        <v>9484.1122183948282</v>
-      </c>
-      <c r="P31" s="146">
-        <f t="shared" si="90"/>
         <v>32536.283269512598</v>
       </c>
       <c r="Q31" s="56">
@@ -13761,11 +13668,11 @@
         <v>46106</v>
       </c>
       <c r="AC31" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD31" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD31" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE31" s="163">
@@ -13795,11 +13702,11 @@
         <v>46106</v>
       </c>
       <c r="AM31" s="77">
+        <f t="shared" si="92"/>
+        <v>0.61189374119541151</v>
+      </c>
+      <c r="AN31" s="76">
         <f t="shared" si="93"/>
-        <v>0.61189374119541151</v>
-      </c>
-      <c r="AN31" s="76">
-        <f t="shared" si="94"/>
         <v>0.38810625880458843</v>
       </c>
       <c r="AO31" s="150">
@@ -13829,12 +13736,12 @@
         <v>46106</v>
       </c>
       <c r="AW31" s="110">
+        <f t="shared" si="94"/>
+        <v>0.6007178594735697</v>
+      </c>
+      <c r="AX31" s="110">
         <f t="shared" si="95"/>
-        <v>0.61453121601044158</v>
-      </c>
-      <c r="AX31" s="110">
-        <f t="shared" si="96"/>
-        <v>0.38546878398955842</v>
+        <v>0.3992821405264303</v>
       </c>
       <c r="AY31" s="111">
         <f t="shared" si="17"/>
@@ -13845,11 +13752,11 @@
       </c>
       <c r="BA31" s="120">
         <f t="shared" si="18"/>
-        <v>5650</v>
+        <v>5523</v>
       </c>
       <c r="BB31" s="113">
-        <f>2973+571</f>
-        <v>3544</v>
+        <f>2973+698</f>
+        <v>3671</v>
       </c>
       <c r="BC31" s="112">
         <v>3904</v>
@@ -13874,15 +13781,15 @@
         <v>46106</v>
       </c>
       <c r="BJ31" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60648223487930564</v>
+      </c>
+      <c r="BK31" s="76">
         <f t="shared" si="97"/>
-        <v>0.60648223487930564</v>
-      </c>
-      <c r="BK31" s="76">
+        <v>0.39351776512069431</v>
+      </c>
+      <c r="BL31" s="79">
         <f t="shared" si="98"/>
-        <v>0.39351776512069431</v>
-      </c>
-      <c r="BL31" s="79">
-        <f t="shared" si="99"/>
         <v>36870</v>
       </c>
       <c r="BM31" s="155">
@@ -13916,51 +13823,51 @@
         <v>56976</v>
       </c>
       <c r="E32" s="159">
-        <f t="shared" si="81"/>
-        <v>0.87234976130300479</v>
+        <f t="shared" si="80"/>
+        <v>0.87012075259758492</v>
       </c>
       <c r="F32" s="87">
         <f t="shared" si="24"/>
-        <v>49703</v>
+        <v>49576</v>
       </c>
       <c r="G32" s="159">
-        <f t="shared" si="82"/>
-        <v>0.12765023869699524</v>
+        <f t="shared" si="81"/>
+        <v>0.12987924740241505</v>
       </c>
       <c r="H32" s="146">
         <f t="shared" si="26"/>
-        <v>7273</v>
+        <v>7400</v>
       </c>
       <c r="I32" s="160">
+        <f t="shared" si="82"/>
+        <v>0.11560657868271626</v>
+      </c>
+      <c r="J32" s="159">
         <f t="shared" si="83"/>
-        <v>0.11560657868271626</v>
-      </c>
-      <c r="J32" s="159">
+        <v>0.15171816254854331</v>
+      </c>
+      <c r="K32" s="159">
         <f t="shared" si="84"/>
-        <v>0.15171816254854331</v>
-      </c>
-      <c r="K32" s="159">
+        <v>0.16739319965126417</v>
+      </c>
+      <c r="L32" s="161">
         <f t="shared" si="85"/>
-        <v>0.16739319965126417</v>
-      </c>
-      <c r="L32" s="161">
+        <v>0.59008556000804546</v>
+      </c>
+      <c r="M32" s="146">
         <f t="shared" si="86"/>
-        <v>0.59008556000804546</v>
-      </c>
-      <c r="M32" s="146">
+        <v>6557.5519626197147</v>
+      </c>
+      <c r="N32" s="146">
         <f t="shared" si="87"/>
-        <v>6557.5519626197147</v>
-      </c>
-      <c r="N32" s="146">
+        <v>8605.9093342410215</v>
+      </c>
+      <c r="O32" s="146">
         <f t="shared" si="88"/>
-        <v>8605.9093342410215</v>
-      </c>
-      <c r="O32" s="146">
+        <v>9495.0444638186582</v>
+      </c>
+      <c r="P32" s="146">
         <f t="shared" si="89"/>
-        <v>9495.0444638186582</v>
-      </c>
-      <c r="P32" s="146">
-        <f t="shared" si="90"/>
         <v>33471.423220336364</v>
       </c>
       <c r="Q32" s="56">
@@ -14002,11 +13909,11 @@
         <v>46107</v>
       </c>
       <c r="AC32" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD32" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD32" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE32" s="163">
@@ -14036,11 +13943,11 @@
         <v>46107</v>
       </c>
       <c r="AM32" s="77">
+        <f t="shared" si="92"/>
+        <v>0.61564348358148069</v>
+      </c>
+      <c r="AN32" s="76">
         <f t="shared" si="93"/>
-        <v>0.61564348358148069</v>
-      </c>
-      <c r="AN32" s="76">
-        <f t="shared" si="94"/>
         <v>0.38435651641851926</v>
       </c>
       <c r="AO32" s="150">
@@ -14070,12 +13977,12 @@
         <v>46107</v>
       </c>
       <c r="AW32" s="169">
+        <f t="shared" si="94"/>
+        <v>0.60601128472222221</v>
+      </c>
+      <c r="AX32" s="169">
         <f t="shared" si="95"/>
-        <v>0.61979166666666663</v>
-      </c>
-      <c r="AX32" s="169">
-        <f t="shared" si="96"/>
-        <v>0.38020833333333331</v>
+        <v>0.39398871527777779</v>
       </c>
       <c r="AY32" s="111">
         <f t="shared" si="17"/>
@@ -14086,11 +13993,11 @@
       </c>
       <c r="BA32" s="120">
         <f t="shared" si="18"/>
-        <v>5712</v>
+        <v>5585</v>
       </c>
       <c r="BB32" s="113">
-        <f>2933+571</f>
-        <v>3504</v>
+        <f>2933+698</f>
+        <v>3631</v>
       </c>
       <c r="BC32" s="112">
         <v>3997</v>
@@ -14115,15 +14022,15 @@
         <v>46107</v>
       </c>
       <c r="BJ32" s="170">
+        <f t="shared" si="96"/>
+        <v>0.60607252418783919</v>
+      </c>
+      <c r="BK32" s="76">
         <f t="shared" si="97"/>
-        <v>0.60607252418783919</v>
-      </c>
-      <c r="BK32" s="76">
+        <v>0.39392747581216075</v>
+      </c>
+      <c r="BL32" s="79">
         <f t="shared" si="98"/>
-        <v>0.39392747581216075</v>
-      </c>
-      <c r="BL32" s="79">
-        <f t="shared" si="99"/>
         <v>38139</v>
       </c>
       <c r="BM32" s="155">
@@ -14157,51 +14064,51 @@
         <v>58724</v>
       </c>
       <c r="E33" s="159">
-        <f t="shared" si="81"/>
-        <v>0.87650704992847894</v>
+        <f t="shared" si="80"/>
+        <v>0.87434439070907977</v>
       </c>
       <c r="F33" s="87">
         <f t="shared" si="24"/>
-        <v>51472</v>
+        <v>51345</v>
       </c>
       <c r="G33" s="159">
-        <f t="shared" si="82"/>
-        <v>0.12349295007152102</v>
+        <f t="shared" si="81"/>
+        <v>0.12565560929092023</v>
       </c>
       <c r="H33" s="146">
         <f t="shared" si="26"/>
-        <v>7252</v>
+        <v>7379</v>
       </c>
       <c r="I33" s="160">
+        <f t="shared" si="82"/>
+        <v>9.0018956306496839E-2</v>
+      </c>
+      <c r="J33" s="159">
         <f t="shared" si="83"/>
-        <v>9.0018956306496839E-2</v>
-      </c>
-      <c r="J33" s="159">
+        <v>0.15400040732559414</v>
+      </c>
+      <c r="K33" s="159">
         <f t="shared" si="84"/>
-        <v>0.15400040732559414</v>
-      </c>
-      <c r="K33" s="159">
+        <v>0.17501407958363271</v>
+      </c>
+      <c r="L33" s="161">
         <f t="shared" si="85"/>
-        <v>0.17501407958363271</v>
-      </c>
-      <c r="L33" s="161">
+        <v>0.61479531888894112</v>
+      </c>
+      <c r="M33" s="146">
         <f t="shared" si="86"/>
-        <v>0.61479531888894112</v>
-      </c>
-      <c r="M33" s="146">
+        <v>5173.4794378906799</v>
+      </c>
+      <c r="N33" s="146">
         <f t="shared" si="87"/>
-        <v>5173.4794378906799</v>
-      </c>
-      <c r="N33" s="146">
+        <v>8850.5574094092208</v>
+      </c>
+      <c r="O33" s="146">
         <f t="shared" si="88"/>
-        <v>8850.5574094092208</v>
-      </c>
-      <c r="O33" s="146">
+        <v>10058.234167750956</v>
+      </c>
+      <c r="P33" s="146">
         <f t="shared" si="89"/>
-        <v>10058.234167750956</v>
-      </c>
-      <c r="P33" s="146">
-        <f t="shared" si="90"/>
         <v>35332.901771866338</v>
       </c>
       <c r="Q33" s="56">
@@ -14243,11 +14150,11 @@
         <v>46108</v>
       </c>
       <c r="AC33" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD33" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD33" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE33" s="163">
@@ -14277,11 +14184,11 @@
         <v>46108</v>
       </c>
       <c r="AM33" s="77">
+        <f t="shared" si="92"/>
+        <v>0.39918616480162766</v>
+      </c>
+      <c r="AN33" s="76">
         <f t="shared" si="93"/>
-        <v>0.39918616480162766</v>
-      </c>
-      <c r="AN33" s="76">
-        <f t="shared" si="94"/>
         <v>0.38738555442522887</v>
       </c>
       <c r="AO33" s="150">
@@ -14310,12 +14217,12 @@
         <v>46108</v>
       </c>
       <c r="AW33" s="169">
+        <f t="shared" si="94"/>
+        <v>0.6037505548158012</v>
+      </c>
+      <c r="AX33" s="169">
         <f t="shared" si="95"/>
-        <v>0.61784287616511313</v>
-      </c>
-      <c r="AX33" s="169">
-        <f t="shared" si="96"/>
-        <v>0.38215712383488681</v>
+        <v>0.39624944518419886</v>
       </c>
       <c r="AY33" s="111">
         <f t="shared" si="17"/>
@@ -14326,11 +14233,11 @@
       </c>
       <c r="BA33" s="120">
         <f t="shared" si="18"/>
-        <v>5568</v>
+        <v>5441</v>
       </c>
       <c r="BB33" s="113">
-        <f>2873+571</f>
-        <v>3444</v>
+        <f>2873+698</f>
+        <v>3571</v>
       </c>
       <c r="BC33" s="112">
         <v>3553</v>
@@ -14355,15 +14262,15 @@
         <v>46108</v>
       </c>
       <c r="BJ33" s="170">
+        <f t="shared" si="96"/>
+        <v>0.60645210610809575</v>
+      </c>
+      <c r="BK33" s="76">
         <f t="shared" si="97"/>
-        <v>0.60645210610809575</v>
-      </c>
-      <c r="BK33" s="76">
+        <v>0.39354789389190431</v>
+      </c>
+      <c r="BL33" s="79">
         <f t="shared" si="98"/>
-        <v>0.39354789389190431</v>
-      </c>
-      <c r="BL33" s="79">
-        <f t="shared" si="99"/>
         <v>39243</v>
       </c>
       <c r="BM33" s="155">
@@ -14397,51 +14304,51 @@
         <v>35834</v>
       </c>
       <c r="E34" s="159">
-        <f t="shared" si="81"/>
-        <v>0.80387341630853382</v>
+        <f t="shared" si="80"/>
+        <v>0.80032929619914051</v>
       </c>
       <c r="F34" s="87">
         <f t="shared" si="24"/>
-        <v>28806</v>
+        <v>28679</v>
       </c>
       <c r="G34" s="159">
-        <f t="shared" si="82"/>
-        <v>0.19612658369146621</v>
+        <f t="shared" si="81"/>
+        <v>0.19967070380085952</v>
       </c>
       <c r="H34" s="146">
         <f t="shared" si="26"/>
-        <v>7028</v>
+        <v>7155</v>
       </c>
       <c r="I34" s="160">
+        <f t="shared" si="82"/>
+        <v>7.4250127097102187E-2</v>
+      </c>
+      <c r="J34" s="159">
         <f t="shared" si="83"/>
-        <v>7.4250127097102187E-2</v>
-      </c>
-      <c r="J34" s="159">
+        <v>0.14865277071682767</v>
+      </c>
+      <c r="K34" s="159">
         <f t="shared" si="84"/>
-        <v>0.14865277071682767</v>
-      </c>
-      <c r="K34" s="159">
+        <v>0.19002670309880146</v>
+      </c>
+      <c r="L34" s="161">
         <f t="shared" si="85"/>
-        <v>0.19002670309880146</v>
-      </c>
-      <c r="L34" s="161">
+        <v>0.62153024911032029</v>
+      </c>
+      <c r="M34" s="146">
         <f t="shared" si="86"/>
-        <v>0.62153024911032029</v>
-      </c>
-      <c r="M34" s="146">
+        <v>2551.01161667514</v>
+      </c>
+      <c r="N34" s="146">
         <f t="shared" si="87"/>
-        <v>2551.01161667514</v>
-      </c>
-      <c r="N34" s="146">
+        <v>5107.2632435180485</v>
+      </c>
+      <c r="O34" s="146">
         <f t="shared" si="88"/>
-        <v>5107.2632435180485</v>
-      </c>
-      <c r="O34" s="146">
+        <v>6528.7474383655217</v>
+      </c>
+      <c r="P34" s="146">
         <f t="shared" si="89"/>
-        <v>6528.7474383655217</v>
-      </c>
-      <c r="P34" s="146">
-        <f t="shared" si="90"/>
         <v>21353.914768683273</v>
       </c>
       <c r="Q34" s="56">
@@ -14483,11 +14390,11 @@
         <v>46109</v>
       </c>
       <c r="AC34" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD34" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD34" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE34" s="163">
@@ -14517,11 +14424,11 @@
         <v>46109</v>
       </c>
       <c r="AM34" s="77">
+        <f t="shared" si="92"/>
+        <v>0.37636798905608754</v>
+      </c>
+      <c r="AN34" s="76">
         <f t="shared" si="93"/>
-        <v>0.37636798905608754</v>
-      </c>
-      <c r="AN34" s="76">
-        <f t="shared" si="94"/>
         <v>0.62363201094391241</v>
       </c>
       <c r="AO34" s="150">
@@ -14551,12 +14458,12 @@
         <v>46109</v>
       </c>
       <c r="AW34" s="110">
+        <f t="shared" si="94"/>
+        <v>0.42679738562091502</v>
+      </c>
+      <c r="AX34" s="110">
         <f t="shared" si="95"/>
-        <v>0.44754901960784316</v>
-      </c>
-      <c r="AX34" s="110">
-        <f t="shared" si="96"/>
-        <v>0.5524509803921569</v>
+        <v>0.57320261437908493</v>
       </c>
       <c r="AY34" s="111">
         <f t="shared" si="17"/>
@@ -14567,11 +14474,11 @@
       </c>
       <c r="BA34" s="120">
         <f t="shared" si="18"/>
-        <v>2739</v>
+        <v>2612</v>
       </c>
       <c r="BB34" s="113">
-        <f>2810+571</f>
-        <v>3381</v>
+        <f>2810+698</f>
+        <v>3508</v>
       </c>
       <c r="BC34" s="112">
         <v>2902</v>
@@ -14596,15 +14503,15 @@
         <v>46109</v>
       </c>
       <c r="BJ34" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60709173448938691</v>
+      </c>
+      <c r="BK34" s="76">
         <f t="shared" si="97"/>
-        <v>0.60709173448938691</v>
-      </c>
-      <c r="BK34" s="76">
+        <v>0.39290826551061309</v>
+      </c>
+      <c r="BL34" s="79">
         <f t="shared" si="98"/>
-        <v>0.39290826551061309</v>
-      </c>
-      <c r="BL34" s="79">
-        <f t="shared" si="99"/>
         <v>24451</v>
       </c>
       <c r="BM34" s="155">
@@ -14638,51 +14545,51 @@
         <v>28890</v>
       </c>
       <c r="E35" s="159">
-        <f t="shared" si="81"/>
-        <v>0.75548632744894428</v>
+        <f t="shared" si="80"/>
+        <v>0.75109034267912778</v>
       </c>
       <c r="F35" s="87">
         <f t="shared" si="24"/>
-        <v>21826</v>
+        <v>21699</v>
       </c>
       <c r="G35" s="159">
-        <f t="shared" si="82"/>
-        <v>0.24451367255105572</v>
+        <f t="shared" si="81"/>
+        <v>0.24890965732087228</v>
       </c>
       <c r="H35" s="146">
         <f t="shared" si="26"/>
-        <v>7064</v>
+        <v>7191</v>
       </c>
       <c r="I35" s="160">
+        <f t="shared" si="82"/>
+        <v>6.4724206286775124E-2</v>
+      </c>
+      <c r="J35" s="159">
         <f t="shared" si="83"/>
-        <v>6.4724206286775124E-2</v>
-      </c>
-      <c r="J35" s="159">
+        <v>0.16336805009282276</v>
+      </c>
+      <c r="K35" s="159">
         <f t="shared" si="84"/>
-        <v>0.16336805009282276</v>
-      </c>
-      <c r="K35" s="159">
+        <v>0.18155468781450021</v>
+      </c>
+      <c r="L35" s="161">
         <f t="shared" si="85"/>
-        <v>0.18155468781450021</v>
-      </c>
-      <c r="L35" s="161">
+        <v>0.62999905603977224</v>
+      </c>
+      <c r="M35" s="146">
         <f t="shared" si="86"/>
-        <v>0.62999905603977224</v>
-      </c>
-      <c r="M35" s="146">
+        <v>1799.5271073912088</v>
+      </c>
+      <c r="N35" s="146">
         <f t="shared" si="87"/>
-        <v>1799.5271073912088</v>
-      </c>
-      <c r="N35" s="146">
+        <v>4542.1218967307514</v>
+      </c>
+      <c r="O35" s="146">
         <f t="shared" si="88"/>
-        <v>4542.1218967307514</v>
-      </c>
-      <c r="O35" s="146">
+        <v>5047.7649853065495</v>
+      </c>
+      <c r="P35" s="146">
         <f t="shared" si="89"/>
-        <v>5047.7649853065495</v>
-      </c>
-      <c r="P35" s="146">
-        <f t="shared" si="90"/>
         <v>17515.863755073788</v>
       </c>
       <c r="Q35" s="56">
@@ -14724,11 +14631,11 @@
         <v>46110</v>
       </c>
       <c r="AC35" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD35" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD35" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE35" s="163">
@@ -14758,11 +14665,11 @@
         <v>46110</v>
       </c>
       <c r="AM35" s="77">
+        <f t="shared" si="92"/>
+        <v>0.30258089368258861</v>
+      </c>
+      <c r="AN35" s="76">
         <f t="shared" si="93"/>
-        <v>0.30258089368258861</v>
-      </c>
-      <c r="AN35" s="76">
-        <f t="shared" si="94"/>
         <v>0.69741910631741144</v>
       </c>
       <c r="AO35" s="150">
@@ -14792,12 +14699,12 @@
         <v>46110</v>
       </c>
       <c r="AW35" s="110">
+        <f t="shared" si="94"/>
+        <v>0.20842572062084258</v>
+      </c>
+      <c r="AX35" s="110">
         <f t="shared" si="95"/>
-        <v>0.23658536585365852</v>
-      </c>
-      <c r="AX35" s="110">
-        <f t="shared" si="96"/>
-        <v>0.76341463414634148</v>
+        <v>0.79157427937915747</v>
       </c>
       <c r="AY35" s="111">
         <f t="shared" si="17"/>
@@ -14808,11 +14715,11 @@
       </c>
       <c r="BA35" s="120">
         <f t="shared" si="18"/>
-        <v>1067</v>
+        <v>940</v>
       </c>
       <c r="BB35" s="113">
-        <f>2872+571</f>
-        <v>3443</v>
+        <f>2872+698</f>
+        <v>3570</v>
       </c>
       <c r="BC35" s="112">
         <v>1556</v>
@@ -14837,15 +14744,15 @@
         <v>46110</v>
       </c>
       <c r="BJ35" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60898012186594741</v>
+      </c>
+      <c r="BK35" s="76">
         <f t="shared" si="97"/>
-        <v>0.60898012186594741</v>
-      </c>
-      <c r="BK35" s="76">
+        <v>0.39101987813405253</v>
+      </c>
+      <c r="BL35" s="79">
         <f t="shared" si="98"/>
-        <v>0.39101987813405253</v>
-      </c>
-      <c r="BL35" s="79">
-        <f t="shared" si="99"/>
         <v>20022</v>
       </c>
       <c r="BM35" s="155">
@@ -14879,35 +14786,35 @@
         <v>56232</v>
       </c>
       <c r="E36" s="159">
-        <f t="shared" si="81"/>
-        <v>0.87010954616588421</v>
+        <f t="shared" si="80"/>
+        <v>0.86785104566794713</v>
       </c>
       <c r="F36" s="87">
         <f t="shared" si="24"/>
-        <v>48928</v>
+        <v>48801</v>
       </c>
       <c r="G36" s="159">
-        <f t="shared" si="82"/>
-        <v>0.12989045383411579</v>
+        <f t="shared" si="81"/>
+        <v>0.13214895433205293</v>
       </c>
       <c r="H36" s="146">
         <f t="shared" si="26"/>
-        <v>7304</v>
+        <v>7431</v>
       </c>
       <c r="I36" s="160">
+        <f t="shared" si="82"/>
+        <v>0.12154377880184332</v>
+      </c>
+      <c r="J36" s="159">
         <f t="shared" si="83"/>
-        <v>0.12154377880184332</v>
-      </c>
-      <c r="J36" s="159">
+        <v>0.16132232462877624</v>
+      </c>
+      <c r="K36" s="159">
         <f t="shared" si="84"/>
-        <v>0.16132232462877624</v>
-      </c>
-      <c r="K36" s="159">
+        <v>0.1718122048337809</v>
+      </c>
+      <c r="L36" s="161">
         <f t="shared" si="85"/>
-        <v>0.1718122048337809</v>
-      </c>
-      <c r="L36" s="161">
-        <f t="shared" si="86"/>
         <v>0.5686923963133641</v>
       </c>
       <c r="M36" s="146">
@@ -14965,11 +14872,11 @@
         <v>46111</v>
       </c>
       <c r="AC36" s="76">
+        <f t="shared" si="90"/>
+        <v>1</v>
+      </c>
+      <c r="AD36" s="162">
         <f t="shared" si="91"/>
-        <v>1</v>
-      </c>
-      <c r="AD36" s="162">
-        <f t="shared" si="92"/>
         <v>0</v>
       </c>
       <c r="AE36" s="163">
@@ -14999,11 +14906,11 @@
         <v>46111</v>
       </c>
       <c r="AM36" s="77">
+        <f t="shared" si="92"/>
+        <v>0.62209878992263434</v>
+      </c>
+      <c r="AN36" s="76">
         <f t="shared" si="93"/>
-        <v>0.62209878992263434</v>
-      </c>
-      <c r="AN36" s="76">
-        <f t="shared" si="94"/>
         <v>0.3779012100773656</v>
       </c>
       <c r="AO36" s="150">
@@ -15033,12 +14940,12 @@
         <v>46111</v>
       </c>
       <c r="AW36" s="110">
+        <f t="shared" si="94"/>
+        <v>0.60967985340088393</v>
+      </c>
+      <c r="AX36" s="110">
         <f t="shared" si="95"/>
-        <v>0.62336962380079763</v>
-      </c>
-      <c r="AX36" s="110">
-        <f t="shared" si="96"/>
-        <v>0.37663037619920231</v>
+        <v>0.39032014659911607</v>
       </c>
       <c r="AY36" s="111">
         <f t="shared" si="17"/>
@@ -15049,11 +14956,11 @@
       </c>
       <c r="BA36" s="120">
         <f t="shared" si="18"/>
-        <v>5783</v>
+        <v>5656</v>
       </c>
       <c r="BB36" s="113">
-        <f>2923+571</f>
-        <v>3494</v>
+        <f>2923+698</f>
+        <v>3621</v>
       </c>
       <c r="BC36" s="112">
         <v>4363</v>
@@ -15078,15 +14985,15 @@
         <v>46111</v>
       </c>
       <c r="BJ36" s="78">
+        <f t="shared" si="96"/>
+        <v>0.60698911116738419</v>
+      </c>
+      <c r="BK36" s="76">
         <f t="shared" si="97"/>
-        <v>0.60698911116738419</v>
-      </c>
-      <c r="BK36" s="76">
+        <v>0.39301088883261587</v>
+      </c>
+      <c r="BL36" s="79">
         <f t="shared" si="98"/>
-        <v>0.39301088883261587</v>
-      </c>
-      <c r="BL36" s="79">
-        <f t="shared" si="99"/>
         <v>35541</v>
       </c>
       <c r="BM36" s="155">
@@ -15118,35 +15025,35 @@
         <v>59138</v>
       </c>
       <c r="E37" s="159">
-        <f t="shared" ref="E37" si="100">F37/D37</f>
-        <v>0.87481822178633029</v>
+        <f t="shared" ref="E37" si="99">F37/D37</f>
+        <v>0.8726707024248368</v>
       </c>
       <c r="F37" s="87">
         <f t="shared" si="24"/>
-        <v>51735</v>
+        <v>51608</v>
       </c>
       <c r="G37" s="159">
-        <f t="shared" ref="G37" si="101">H37/D37</f>
-        <v>0.12518177821366971</v>
+        <f t="shared" ref="G37" si="100">H37/D37</f>
+        <v>0.12732929757516318</v>
       </c>
       <c r="H37" s="146">
         <f t="shared" si="26"/>
-        <v>7403</v>
+        <v>7530</v>
       </c>
       <c r="I37" s="160">
-        <f t="shared" ref="I37" si="102">AE37/(AE37+AO37+BL37+AY37)</f>
+        <f t="shared" ref="I37" si="101">AE37/(AE37+AO37+BL37+AY37)</f>
         <v>0.11750829452409217</v>
       </c>
       <c r="J37" s="159">
-        <f t="shared" ref="J37" si="103">AO37/(AE37+AO37+BL37+AY37)</f>
+        <f t="shared" ref="J37" si="102">AO37/(AE37+AO37+BL37+AY37)</f>
         <v>0.1568958694791952</v>
       </c>
       <c r="K37" s="159">
-        <f t="shared" ref="K37" si="104">AY37/(AF37+AP37+BM37+AZ37+AY37)</f>
+        <f t="shared" ref="K37" si="103">AY37/(AF37+AP37+BM37+AZ37+AY37)</f>
         <v>0.16410063837776942</v>
       </c>
       <c r="L37" s="161">
-        <f t="shared" ref="L37" si="105">BL37/(AE37+AO37+BL37+AY37)</f>
+        <f t="shared" ref="L37" si="104">BL37/(AE37+AO37+BL37+AY37)</f>
         <v>0.58592822573280978</v>
       </c>
       <c r="M37" s="146">
@@ -15204,18 +15111,18 @@
         <v>46112</v>
       </c>
       <c r="AC37" s="76">
-        <f t="shared" ref="AC37" si="106">+AF37/AE37</f>
+        <f t="shared" ref="AC37" si="105">+AF37/AE37</f>
         <v>1</v>
       </c>
       <c r="AD37" s="162">
-        <f t="shared" ref="AD37" si="107">+AG37/AE37</f>
+        <f t="shared" ref="AD37" si="106">+AG37/AE37</f>
         <v>0</v>
       </c>
       <c r="AE37" s="163">
         <v>7721</v>
       </c>
       <c r="AF37" s="118">
-        <f t="shared" ref="AF37" si="108">+AE37-AG37</f>
+        <f t="shared" ref="AF37" si="107">+AE37-AG37</f>
         <v>7721</v>
       </c>
       <c r="AG37" s="147">
@@ -15238,18 +15145,18 @@
         <v>46112</v>
       </c>
       <c r="AM37" s="77">
-        <f t="shared" ref="AM37" si="109">+AP37/AO37</f>
+        <f t="shared" ref="AM37" si="108">+AP37/AO37</f>
         <v>0.62692792705403044</v>
       </c>
       <c r="AN37" s="76">
-        <f t="shared" ref="AN37" si="110">+AQ37/AO37</f>
+        <f t="shared" ref="AN37" si="109">+AQ37/AO37</f>
         <v>0.37307207294596956</v>
       </c>
       <c r="AO37" s="150">
         <v>10309</v>
       </c>
       <c r="AP37" s="117">
-        <f t="shared" ref="AP37" si="111">AO37-AQ37</f>
+        <f t="shared" ref="AP37" si="110">AO37-AQ37</f>
         <v>6463</v>
       </c>
       <c r="AQ37" s="151">
@@ -15272,12 +15179,12 @@
         <v>46112</v>
       </c>
       <c r="AW37" s="110">
-        <f t="shared" ref="AW37" si="112">BA37/AZ37</f>
-        <v>0.61240056663397624</v>
+        <f t="shared" ref="AW37" si="111">BA37/AZ37</f>
+        <v>0.59856162144491665</v>
       </c>
       <c r="AX37" s="110">
-        <f t="shared" ref="AX37" si="113">BB37/AZ37</f>
-        <v>0.38759943336602376</v>
+        <f t="shared" ref="AX37" si="112">BB37/AZ37</f>
+        <v>0.40143837855508335</v>
       </c>
       <c r="AY37" s="111">
         <f t="shared" si="17"/>
@@ -15288,11 +15195,11 @@
       </c>
       <c r="BA37" s="120">
         <f t="shared" si="18"/>
-        <v>5620</v>
+        <v>5493</v>
       </c>
       <c r="BB37" s="113">
-        <f>2986+571</f>
-        <v>3557</v>
+        <f>2986+698</f>
+        <v>3684</v>
       </c>
       <c r="BC37" s="112">
         <v>4381</v>
@@ -15317,15 +15224,15 @@
         <v>46112</v>
       </c>
       <c r="BJ37" s="78">
-        <f t="shared" ref="BJ37" si="114">+BM37/BL37</f>
+        <f t="shared" ref="BJ37" si="113">+BM37/BL37</f>
         <v>0.60741837450323388</v>
       </c>
       <c r="BK37" s="76">
-        <f t="shared" ref="BK37" si="115">+BN37/BL37</f>
+        <f t="shared" ref="BK37" si="114">+BN37/BL37</f>
         <v>0.39258162549676617</v>
       </c>
       <c r="BL37" s="79">
-        <f t="shared" ref="BL37" si="116">BM37+BN37</f>
+        <f t="shared" ref="BL37" si="115">BM37+BN37</f>
         <v>38499</v>
       </c>
       <c r="BM37" s="155">
@@ -15367,6 +15274,22 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="D1:P2"/>
+    <mergeCell ref="R1:AA2"/>
+    <mergeCell ref="AC1:AK2"/>
+    <mergeCell ref="AM1:AU2"/>
+    <mergeCell ref="AO3:AQ3"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:AA3"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AG3"/>
+    <mergeCell ref="AH3:AK3"/>
+    <mergeCell ref="AM3:AM4"/>
     <mergeCell ref="BJ1:BR2"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
@@ -15383,22 +15306,6 @@
     <mergeCell ref="AX3:AX4"/>
     <mergeCell ref="AY3:BB3"/>
     <mergeCell ref="BC3:BH3"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="D1:P2"/>
-    <mergeCell ref="R1:AA2"/>
-    <mergeCell ref="AC1:AK2"/>
-    <mergeCell ref="AM1:AU2"/>
-    <mergeCell ref="AO3:AQ3"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:AA3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AG3"/>
-    <mergeCell ref="AH3:AK3"/>
-    <mergeCell ref="AM3:AM4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="88" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
@@ -19537,6 +19444,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+    <SharedWithUsers xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100E3C748FF7EC2ED4E8EAD43CD1EEC2D0E" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="ea203103aa5aa41fa7dd49b43cb8a2de">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xmlns:ns3="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49b0a91519af75797ffa607b75695ffb" ns2:_="" ns3:_="">
     <xsd:import namespace="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
@@ -19783,43 +19719,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <C_x00f3_digo xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-    <SharedWithUsers xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ffac592c-cdc9-47d3-9b5f-572462ebd9e4" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="a49c09fe-4018-4f3a-9927-d6e5af32fdd5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43069561-89A9-4F0F-93A7-F4E1BB90CC53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244A8360-A9F5-4BD3-90CB-4CB82EE20B09}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37B2135A-E44A-4FCA-87FA-9A4760BEC53A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37B2135A-E44A-4FCA-87FA-9A4760BEC53A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244A8360-A9F5-4BD3-90CB-4CB82EE20B09}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43069561-89A9-4F0F-93A7-F4E1BB90CC53}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a49c09fe-4018-4f3a-9927-d6e5af32fdd5"/>
+    <ds:schemaRef ds:uri="ffac592c-cdc9-47d3-9b5f-572462ebd9e4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>